--- a/template.xlsx
+++ b/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A01CA920-E19F-4ED4-B5C8-9602E0E759AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFD01F7-0612-497E-8BE7-31D6603724DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,31 +94,6 @@
     <t>Number of backwashes during this month:</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Bridgeport Public Utility District - Monthly Treatment </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Field Kit Data</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Report</t>
-    </r>
-  </si>
-  <si>
     <t>Bridgeport Public Utility District</t>
   </si>
   <si>
@@ -133,6 +108,9 @@
   <si>
     <t>FE Tank (Inches)</t>
   </si>
+  <si>
+    <t>Bridgeport Public Utility District - Monthly Treatment Field Kit Data Report</t>
+  </si>
 </sst>
 </file>
 
@@ -142,7 +120,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\-yy"/>
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,29 +174,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -252,6 +207,22 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -461,7 +432,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -551,15 +522,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="12" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -578,39 +573,15 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="12" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -838,16 +809,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
-        <v>21</v>
+      <c r="A1" s="50" t="s">
+        <v>26</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
@@ -892,7 +863,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="52" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
@@ -904,7 +875,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
@@ -914,7 +885,7 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="7"/>
       <c r="C7" s="10"/>
       <c r="D7" s="9"/>
@@ -924,7 +895,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+      <c r="A8" s="54"/>
       <c r="B8" s="7"/>
       <c r="C8" s="10"/>
       <c r="D8" s="9"/>
@@ -934,7 +905,7 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="55" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="11"/>
@@ -946,7 +917,7 @@
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="43"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
       <c r="D10" s="13"/>
@@ -956,7 +927,7 @@
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="43"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
       <c r="D11" s="13"/>
@@ -966,7 +937,7 @@
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12"/>
       <c r="D12" s="13"/>
@@ -976,7 +947,7 @@
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="56" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="14"/>
@@ -988,7 +959,7 @@
       <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="14"/>
       <c r="C14" s="15"/>
       <c r="D14" s="16"/>
@@ -998,7 +969,7 @@
       <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="43"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="14"/>
       <c r="C15" s="18"/>
       <c r="D15" s="19"/>
@@ -1008,7 +979,7 @@
       <c r="H15" s="17"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="14"/>
       <c r="C16" s="18"/>
       <c r="D16" s="19"/>
@@ -1018,7 +989,7 @@
       <c r="H16" s="17"/>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="47" t="s">
+      <c r="A17" s="57" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="20"/>
@@ -1030,7 +1001,7 @@
       <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="43"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
       <c r="D18" s="22"/>
@@ -1040,7 +1011,7 @@
       <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="43"/>
+      <c r="A19" s="53"/>
       <c r="B19" s="20"/>
       <c r="C19" s="22"/>
       <c r="D19" s="22"/>
@@ -1050,7 +1021,7 @@
       <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="20"/>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
@@ -1075,13 +1046,13 @@
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="37" t="s">
+      <c r="E22" s="59" t="s">
         <v>20</v>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="23"/>
       <c r="H22" s="23"/>
-      <c r="I22" s="38"/>
+      <c r="I22" s="60"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
@@ -1103,7 +1074,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="1"/>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="58" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="26"/>
@@ -9897,4229 +9868,4229 @@
   <dimension ref="B1:E1000"/>
   <sheetFormatPr defaultColWidth="12.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="50" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" style="50" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" style="50" customWidth="1"/>
-    <col min="4" max="26" width="9.7109375" style="50" customWidth="1"/>
-    <col min="27" max="16384" width="12.85546875" style="50"/>
+    <col min="1" max="1" width="6.28515625" style="37" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" style="37" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="37" customWidth="1"/>
+    <col min="4" max="26" width="9.7109375" style="37" customWidth="1"/>
+    <col min="27" max="16384" width="12.85546875" style="37"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B1" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="49"/>
+    </row>
+    <row r="2" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="49"/>
-    </row>
-    <row r="2" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="C2" s="49"/>
+    </row>
+    <row r="3" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+    </row>
+    <row r="4" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B4" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="49"/>
-    </row>
-    <row r="3" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-    </row>
-    <row r="4" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="53" t="s">
+    </row>
+    <row r="5" spans="2:5" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="41"/>
+      <c r="C5" s="42"/>
+    </row>
+    <row r="6" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="43" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-    </row>
-    <row r="6" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="56" t="s">
+      <c r="C6" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="57" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="7" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="58">
+      <c r="B7" s="45">
         <v>46113</v>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="46">
         <v>33.75</v>
       </c>
-      <c r="D7" s="60"/>
+      <c r="D7" s="47"/>
     </row>
     <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="58">
+      <c r="B8" s="45">
         <f t="shared" ref="B8:B36" si="0">B7+1</f>
         <v>46114</v>
       </c>
-      <c r="C8" s="59">
+      <c r="C8" s="46">
         <v>33.5</v>
       </c>
-      <c r="D8" s="60"/>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="58">
+      <c r="B9" s="45">
         <f t="shared" si="0"/>
         <v>46115</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="46">
         <v>33.75</v>
       </c>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
     </row>
     <row r="10" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="58">
+      <c r="B10" s="45">
         <f t="shared" si="0"/>
         <v>46116</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="46">
         <v>32.5</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
     </row>
     <row r="11" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="58">
+      <c r="B11" s="45">
         <f t="shared" si="0"/>
         <v>46117</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="46">
         <v>32.25</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
     </row>
     <row r="12" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="58">
+      <c r="B12" s="45">
         <f t="shared" si="0"/>
         <v>46118</v>
       </c>
-      <c r="C12" s="59">
+      <c r="C12" s="46">
         <v>31.75</v>
       </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
     </row>
     <row r="13" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="58">
+      <c r="B13" s="45">
         <f t="shared" si="0"/>
         <v>46119</v>
       </c>
-      <c r="C13" s="59">
+      <c r="C13" s="46">
         <v>31.75</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
     </row>
     <row r="14" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="58">
+      <c r="B14" s="45">
         <f t="shared" si="0"/>
         <v>46120</v>
       </c>
-      <c r="C14" s="59">
+      <c r="C14" s="46">
         <v>30.75</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
     </row>
     <row r="15" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="58">
+      <c r="B15" s="45">
         <f t="shared" si="0"/>
         <v>46121</v>
       </c>
-      <c r="C15" s="59">
+      <c r="C15" s="46">
         <v>30.5</v>
       </c>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
     </row>
     <row r="16" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="58">
+      <c r="B16" s="45">
         <f t="shared" si="0"/>
         <v>46122</v>
       </c>
-      <c r="C16" s="59">
+      <c r="C16" s="46">
         <v>30</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
     </row>
     <row r="17" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="58">
+      <c r="B17" s="45">
         <f t="shared" si="0"/>
         <v>46123</v>
       </c>
-      <c r="C17" s="59">
+      <c r="C17" s="46">
         <v>29.5</v>
       </c>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
     </row>
     <row r="18" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="58">
+      <c r="B18" s="45">
         <f t="shared" si="0"/>
         <v>46124</v>
       </c>
-      <c r="C18" s="59">
+      <c r="C18" s="46">
         <v>28.75</v>
       </c>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
     </row>
     <row r="19" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="58">
+      <c r="B19" s="45">
         <f t="shared" si="0"/>
         <v>46125</v>
       </c>
-      <c r="C19" s="59">
+      <c r="C19" s="46">
         <v>28.5</v>
       </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
     </row>
     <row r="20" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="58">
+      <c r="B20" s="45">
         <f t="shared" si="0"/>
         <v>46126</v>
       </c>
-      <c r="C20" s="59">
+      <c r="C20" s="46">
         <v>28</v>
       </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
     </row>
     <row r="21" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="58">
+      <c r="B21" s="45">
         <f t="shared" si="0"/>
         <v>46127</v>
       </c>
-      <c r="C21" s="59">
+      <c r="C21" s="46">
         <v>27.5</v>
       </c>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
     </row>
     <row r="22" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="58">
+      <c r="B22" s="45">
         <f t="shared" si="0"/>
         <v>46128</v>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="46">
         <v>27</v>
       </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
     </row>
     <row r="23" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="58">
+      <c r="B23" s="45">
         <f t="shared" si="0"/>
         <v>46129</v>
       </c>
-      <c r="C23" s="59">
+      <c r="C23" s="46">
         <v>26.5</v>
       </c>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="58">
+      <c r="B24" s="45">
         <f t="shared" si="0"/>
         <v>46130</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="46">
         <v>24.75</v>
       </c>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
     </row>
     <row r="25" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="58">
+      <c r="B25" s="45">
         <f t="shared" si="0"/>
         <v>46131</v>
       </c>
-      <c r="C25" s="59">
+      <c r="C25" s="46">
         <v>25.375</v>
       </c>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
     </row>
     <row r="26" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="58">
+      <c r="B26" s="45">
         <f t="shared" si="0"/>
         <v>46132</v>
       </c>
-      <c r="C26" s="59">
+      <c r="C26" s="46">
         <v>24.75</v>
       </c>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
     </row>
     <row r="27" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="58">
+      <c r="B27" s="45">
         <f t="shared" si="0"/>
         <v>46133</v>
       </c>
-      <c r="C27" s="59">
+      <c r="C27" s="46">
         <v>24.25</v>
       </c>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
     </row>
     <row r="28" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="58">
+      <c r="B28" s="45">
         <f t="shared" si="0"/>
         <v>46134</v>
       </c>
-      <c r="C28" s="59">
+      <c r="C28" s="46">
         <v>23.75</v>
       </c>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
     </row>
     <row r="29" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="58">
+      <c r="B29" s="45">
         <f t="shared" si="0"/>
         <v>46135</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="46">
         <v>23.25</v>
       </c>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
     </row>
     <row r="30" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="58">
+      <c r="B30" s="45">
         <f t="shared" si="0"/>
         <v>46136</v>
       </c>
-      <c r="C30" s="59">
+      <c r="C30" s="46">
         <v>22.5</v>
       </c>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="47"/>
     </row>
     <row r="31" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="58">
+      <c r="B31" s="45">
         <f t="shared" si="0"/>
         <v>46137</v>
       </c>
-      <c r="C31" s="59">
+      <c r="C31" s="46">
         <v>22</v>
       </c>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
     </row>
     <row r="32" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="58">
+      <c r="B32" s="45">
         <f t="shared" si="0"/>
         <v>46138</v>
       </c>
-      <c r="C32" s="59">
+      <c r="C32" s="46">
         <v>21.5</v>
       </c>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
     </row>
     <row r="33" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="58">
+      <c r="B33" s="45">
         <f t="shared" si="0"/>
         <v>46139</v>
       </c>
-      <c r="C33" s="59">
+      <c r="C33" s="46">
         <v>21</v>
       </c>
-      <c r="D33" s="60"/>
-      <c r="E33" s="60"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
     </row>
     <row r="34" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="58">
+      <c r="B34" s="45">
         <f t="shared" si="0"/>
         <v>46140</v>
       </c>
-      <c r="C34" s="59">
+      <c r="C34" s="46">
         <v>20.5</v>
       </c>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
     </row>
     <row r="35" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="58">
+      <c r="B35" s="45">
         <f t="shared" si="0"/>
         <v>46141</v>
       </c>
-      <c r="C35" s="59">
+      <c r="C35" s="46">
         <v>19.5</v>
       </c>
-      <c r="D35" s="60"/>
-      <c r="E35" s="60"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
     </row>
     <row r="36" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="58">
+      <c r="B36" s="45">
         <f t="shared" si="0"/>
         <v>46142</v>
       </c>
-      <c r="C36" s="59">
+      <c r="C36" s="46">
         <v>18.75</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="54"/>
-      <c r="C37" s="55"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="42"/>
     </row>
     <row r="38" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="54"/>
-      <c r="C38" s="55"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="42"/>
     </row>
     <row r="39" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="54"/>
-      <c r="C39" s="55"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="42"/>
     </row>
     <row r="40" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="54"/>
-      <c r="C40" s="55"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="42"/>
     </row>
     <row r="41" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="54"/>
-      <c r="C41" s="55"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="42"/>
     </row>
     <row r="42" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="54"/>
-      <c r="C42" s="55"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="42"/>
     </row>
     <row r="43" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="54"/>
-      <c r="C43" s="55"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="42"/>
     </row>
     <row r="44" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="54"/>
-      <c r="C44" s="55"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="42"/>
     </row>
     <row r="45" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="54"/>
-      <c r="C45" s="55"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="42"/>
     </row>
     <row r="46" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="54"/>
-      <c r="C46" s="55"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="42"/>
     </row>
     <row r="47" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="54"/>
-      <c r="C47" s="55"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="42"/>
     </row>
     <row r="48" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="54"/>
-      <c r="C48" s="55"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="42"/>
     </row>
     <row r="49" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="54"/>
-      <c r="C49" s="55"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="42"/>
     </row>
     <row r="50" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="54"/>
-      <c r="C50" s="55"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="42"/>
     </row>
     <row r="51" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="54"/>
-      <c r="C51" s="55"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="42"/>
     </row>
     <row r="52" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="54"/>
-      <c r="C52" s="55"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="42"/>
     </row>
     <row r="53" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="54"/>
-      <c r="C53" s="55"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="42"/>
     </row>
     <row r="54" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="54"/>
-      <c r="C54" s="55"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="42"/>
     </row>
     <row r="55" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="54"/>
-      <c r="C55" s="55"/>
+      <c r="B55" s="41"/>
+      <c r="C55" s="42"/>
     </row>
     <row r="56" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="54"/>
-      <c r="C56" s="55"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="42"/>
     </row>
     <row r="57" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="54"/>
-      <c r="C57" s="55"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="42"/>
     </row>
     <row r="58" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="54"/>
-      <c r="C58" s="55"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="42"/>
     </row>
     <row r="59" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="54"/>
-      <c r="C59" s="55"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="42"/>
     </row>
     <row r="60" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="54"/>
-      <c r="C60" s="55"/>
+      <c r="B60" s="41"/>
+      <c r="C60" s="42"/>
     </row>
     <row r="61" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="54"/>
-      <c r="C61" s="55"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="42"/>
     </row>
     <row r="62" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="54"/>
-      <c r="C62" s="55"/>
+      <c r="B62" s="41"/>
+      <c r="C62" s="42"/>
     </row>
     <row r="63" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="54"/>
-      <c r="C63" s="55"/>
+      <c r="B63" s="41"/>
+      <c r="C63" s="42"/>
     </row>
     <row r="64" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="54"/>
-      <c r="C64" s="55"/>
+      <c r="B64" s="41"/>
+      <c r="C64" s="42"/>
     </row>
     <row r="65" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B65" s="54"/>
-      <c r="C65" s="55"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="42"/>
     </row>
     <row r="66" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="54"/>
-      <c r="C66" s="55"/>
+      <c r="B66" s="41"/>
+      <c r="C66" s="42"/>
     </row>
     <row r="67" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="54"/>
-      <c r="C67" s="55"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="42"/>
     </row>
     <row r="68" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="54"/>
-      <c r="C68" s="55"/>
+      <c r="B68" s="41"/>
+      <c r="C68" s="42"/>
     </row>
     <row r="69" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="54"/>
-      <c r="C69" s="55"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="42"/>
     </row>
     <row r="70" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="54"/>
-      <c r="C70" s="55"/>
+      <c r="B70" s="41"/>
+      <c r="C70" s="42"/>
     </row>
     <row r="71" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="54"/>
-      <c r="C71" s="55"/>
+      <c r="B71" s="41"/>
+      <c r="C71" s="42"/>
     </row>
     <row r="72" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B72" s="54"/>
-      <c r="C72" s="55"/>
+      <c r="B72" s="41"/>
+      <c r="C72" s="42"/>
     </row>
     <row r="73" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="54"/>
-      <c r="C73" s="55"/>
+      <c r="B73" s="41"/>
+      <c r="C73" s="42"/>
     </row>
     <row r="74" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="54"/>
-      <c r="C74" s="55"/>
+      <c r="B74" s="41"/>
+      <c r="C74" s="42"/>
     </row>
     <row r="75" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="54"/>
-      <c r="C75" s="55"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="42"/>
     </row>
     <row r="76" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="54"/>
-      <c r="C76" s="55"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="42"/>
     </row>
     <row r="77" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B77" s="54"/>
-      <c r="C77" s="55"/>
+      <c r="B77" s="41"/>
+      <c r="C77" s="42"/>
     </row>
     <row r="78" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="54"/>
-      <c r="C78" s="55"/>
+      <c r="B78" s="41"/>
+      <c r="C78" s="42"/>
     </row>
     <row r="79" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="54"/>
-      <c r="C79" s="55"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="42"/>
     </row>
     <row r="80" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B80" s="54"/>
-      <c r="C80" s="55"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="42"/>
     </row>
     <row r="81" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="54"/>
-      <c r="C81" s="55"/>
+      <c r="B81" s="41"/>
+      <c r="C81" s="42"/>
     </row>
     <row r="82" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B82" s="54"/>
-      <c r="C82" s="55"/>
+      <c r="B82" s="41"/>
+      <c r="C82" s="42"/>
     </row>
     <row r="83" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B83" s="54"/>
-      <c r="C83" s="55"/>
+      <c r="B83" s="41"/>
+      <c r="C83" s="42"/>
     </row>
     <row r="84" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="54"/>
-      <c r="C84" s="55"/>
+      <c r="B84" s="41"/>
+      <c r="C84" s="42"/>
     </row>
     <row r="85" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B85" s="54"/>
-      <c r="C85" s="55"/>
+      <c r="B85" s="41"/>
+      <c r="C85" s="42"/>
     </row>
     <row r="86" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="54"/>
-      <c r="C86" s="55"/>
+      <c r="B86" s="41"/>
+      <c r="C86" s="42"/>
     </row>
     <row r="87" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="54"/>
-      <c r="C87" s="55"/>
+      <c r="B87" s="41"/>
+      <c r="C87" s="42"/>
     </row>
     <row r="88" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="54"/>
-      <c r="C88" s="55"/>
+      <c r="B88" s="41"/>
+      <c r="C88" s="42"/>
     </row>
     <row r="89" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="54"/>
-      <c r="C89" s="55"/>
+      <c r="B89" s="41"/>
+      <c r="C89" s="42"/>
     </row>
     <row r="90" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="54"/>
-      <c r="C90" s="55"/>
+      <c r="B90" s="41"/>
+      <c r="C90" s="42"/>
     </row>
     <row r="91" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="54"/>
-      <c r="C91" s="55"/>
+      <c r="B91" s="41"/>
+      <c r="C91" s="42"/>
     </row>
     <row r="92" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="54"/>
-      <c r="C92" s="55"/>
+      <c r="B92" s="41"/>
+      <c r="C92" s="42"/>
     </row>
     <row r="93" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B93" s="54"/>
-      <c r="C93" s="55"/>
+      <c r="B93" s="41"/>
+      <c r="C93" s="42"/>
     </row>
     <row r="94" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B94" s="54"/>
-      <c r="C94" s="55"/>
+      <c r="B94" s="41"/>
+      <c r="C94" s="42"/>
     </row>
     <row r="95" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="54"/>
-      <c r="C95" s="55"/>
+      <c r="B95" s="41"/>
+      <c r="C95" s="42"/>
     </row>
     <row r="96" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="54"/>
-      <c r="C96" s="55"/>
+      <c r="B96" s="41"/>
+      <c r="C96" s="42"/>
     </row>
     <row r="97" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="54"/>
-      <c r="C97" s="55"/>
+      <c r="B97" s="41"/>
+      <c r="C97" s="42"/>
     </row>
     <row r="98" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B98" s="54"/>
-      <c r="C98" s="55"/>
+      <c r="B98" s="41"/>
+      <c r="C98" s="42"/>
     </row>
     <row r="99" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B99" s="54"/>
-      <c r="C99" s="55"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="42"/>
     </row>
     <row r="100" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B100" s="54"/>
-      <c r="C100" s="55"/>
+      <c r="B100" s="41"/>
+      <c r="C100" s="42"/>
     </row>
     <row r="101" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B101" s="54"/>
-      <c r="C101" s="55"/>
+      <c r="B101" s="41"/>
+      <c r="C101" s="42"/>
     </row>
     <row r="102" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B102" s="54"/>
-      <c r="C102" s="55"/>
+      <c r="B102" s="41"/>
+      <c r="C102" s="42"/>
     </row>
     <row r="103" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B103" s="54"/>
-      <c r="C103" s="55"/>
+      <c r="B103" s="41"/>
+      <c r="C103" s="42"/>
     </row>
     <row r="104" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B104" s="54"/>
-      <c r="C104" s="55"/>
+      <c r="B104" s="41"/>
+      <c r="C104" s="42"/>
     </row>
     <row r="105" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B105" s="54"/>
-      <c r="C105" s="55"/>
+      <c r="B105" s="41"/>
+      <c r="C105" s="42"/>
     </row>
     <row r="106" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B106" s="54"/>
-      <c r="C106" s="55"/>
+      <c r="B106" s="41"/>
+      <c r="C106" s="42"/>
     </row>
     <row r="107" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B107" s="54"/>
-      <c r="C107" s="55"/>
+      <c r="B107" s="41"/>
+      <c r="C107" s="42"/>
     </row>
     <row r="108" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B108" s="54"/>
-      <c r="C108" s="55"/>
+      <c r="B108" s="41"/>
+      <c r="C108" s="42"/>
     </row>
     <row r="109" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B109" s="54"/>
-      <c r="C109" s="55"/>
+      <c r="B109" s="41"/>
+      <c r="C109" s="42"/>
     </row>
     <row r="110" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B110" s="54"/>
-      <c r="C110" s="55"/>
+      <c r="B110" s="41"/>
+      <c r="C110" s="42"/>
     </row>
     <row r="111" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B111" s="54"/>
-      <c r="C111" s="55"/>
+      <c r="B111" s="41"/>
+      <c r="C111" s="42"/>
     </row>
     <row r="112" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B112" s="54"/>
-      <c r="C112" s="55"/>
+      <c r="B112" s="41"/>
+      <c r="C112" s="42"/>
     </row>
     <row r="113" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B113" s="54"/>
-      <c r="C113" s="55"/>
+      <c r="B113" s="41"/>
+      <c r="C113" s="42"/>
     </row>
     <row r="114" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B114" s="54"/>
-      <c r="C114" s="55"/>
+      <c r="B114" s="41"/>
+      <c r="C114" s="42"/>
     </row>
     <row r="115" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B115" s="54"/>
-      <c r="C115" s="55"/>
+      <c r="B115" s="41"/>
+      <c r="C115" s="42"/>
     </row>
     <row r="116" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B116" s="54"/>
-      <c r="C116" s="55"/>
+      <c r="B116" s="41"/>
+      <c r="C116" s="42"/>
     </row>
     <row r="117" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B117" s="54"/>
-      <c r="C117" s="55"/>
+      <c r="B117" s="41"/>
+      <c r="C117" s="42"/>
     </row>
     <row r="118" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B118" s="54"/>
-      <c r="C118" s="55"/>
+      <c r="B118" s="41"/>
+      <c r="C118" s="42"/>
     </row>
     <row r="119" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B119" s="54"/>
-      <c r="C119" s="55"/>
+      <c r="B119" s="41"/>
+      <c r="C119" s="42"/>
     </row>
     <row r="120" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B120" s="54"/>
-      <c r="C120" s="55"/>
+      <c r="B120" s="41"/>
+      <c r="C120" s="42"/>
     </row>
     <row r="121" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B121" s="54"/>
-      <c r="C121" s="55"/>
+      <c r="B121" s="41"/>
+      <c r="C121" s="42"/>
     </row>
     <row r="122" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B122" s="54"/>
-      <c r="C122" s="55"/>
+      <c r="B122" s="41"/>
+      <c r="C122" s="42"/>
     </row>
     <row r="123" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B123" s="54"/>
-      <c r="C123" s="55"/>
+      <c r="B123" s="41"/>
+      <c r="C123" s="42"/>
     </row>
     <row r="124" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B124" s="54"/>
-      <c r="C124" s="55"/>
+      <c r="B124" s="41"/>
+      <c r="C124" s="42"/>
     </row>
     <row r="125" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B125" s="54"/>
-      <c r="C125" s="55"/>
+      <c r="B125" s="41"/>
+      <c r="C125" s="42"/>
     </row>
     <row r="126" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B126" s="54"/>
-      <c r="C126" s="55"/>
+      <c r="B126" s="41"/>
+      <c r="C126" s="42"/>
     </row>
     <row r="127" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B127" s="54"/>
-      <c r="C127" s="55"/>
+      <c r="B127" s="41"/>
+      <c r="C127" s="42"/>
     </row>
     <row r="128" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B128" s="54"/>
-      <c r="C128" s="55"/>
+      <c r="B128" s="41"/>
+      <c r="C128" s="42"/>
     </row>
     <row r="129" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B129" s="54"/>
-      <c r="C129" s="55"/>
+      <c r="B129" s="41"/>
+      <c r="C129" s="42"/>
     </row>
     <row r="130" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B130" s="54"/>
-      <c r="C130" s="55"/>
+      <c r="B130" s="41"/>
+      <c r="C130" s="42"/>
     </row>
     <row r="131" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B131" s="54"/>
-      <c r="C131" s="55"/>
+      <c r="B131" s="41"/>
+      <c r="C131" s="42"/>
     </row>
     <row r="132" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B132" s="54"/>
-      <c r="C132" s="55"/>
+      <c r="B132" s="41"/>
+      <c r="C132" s="42"/>
     </row>
     <row r="133" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B133" s="54"/>
-      <c r="C133" s="55"/>
+      <c r="B133" s="41"/>
+      <c r="C133" s="42"/>
     </row>
     <row r="134" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B134" s="54"/>
-      <c r="C134" s="55"/>
+      <c r="B134" s="41"/>
+      <c r="C134" s="42"/>
     </row>
     <row r="135" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B135" s="54"/>
-      <c r="C135" s="55"/>
+      <c r="B135" s="41"/>
+      <c r="C135" s="42"/>
     </row>
     <row r="136" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B136" s="54"/>
-      <c r="C136" s="55"/>
+      <c r="B136" s="41"/>
+      <c r="C136" s="42"/>
     </row>
     <row r="137" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B137" s="54"/>
-      <c r="C137" s="55"/>
+      <c r="B137" s="41"/>
+      <c r="C137" s="42"/>
     </row>
     <row r="138" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B138" s="54"/>
-      <c r="C138" s="55"/>
+      <c r="B138" s="41"/>
+      <c r="C138" s="42"/>
     </row>
     <row r="139" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B139" s="54"/>
-      <c r="C139" s="55"/>
+      <c r="B139" s="41"/>
+      <c r="C139" s="42"/>
     </row>
     <row r="140" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B140" s="54"/>
-      <c r="C140" s="55"/>
+      <c r="B140" s="41"/>
+      <c r="C140" s="42"/>
     </row>
     <row r="141" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B141" s="54"/>
-      <c r="C141" s="55"/>
+      <c r="B141" s="41"/>
+      <c r="C141" s="42"/>
     </row>
     <row r="142" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B142" s="54"/>
-      <c r="C142" s="55"/>
+      <c r="B142" s="41"/>
+      <c r="C142" s="42"/>
     </row>
     <row r="143" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B143" s="54"/>
-      <c r="C143" s="55"/>
+      <c r="B143" s="41"/>
+      <c r="C143" s="42"/>
     </row>
     <row r="144" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B144" s="54"/>
-      <c r="C144" s="55"/>
+      <c r="B144" s="41"/>
+      <c r="C144" s="42"/>
     </row>
     <row r="145" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B145" s="54"/>
-      <c r="C145" s="55"/>
+      <c r="B145" s="41"/>
+      <c r="C145" s="42"/>
     </row>
     <row r="146" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B146" s="54"/>
-      <c r="C146" s="55"/>
+      <c r="B146" s="41"/>
+      <c r="C146" s="42"/>
     </row>
     <row r="147" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B147" s="54"/>
-      <c r="C147" s="55"/>
+      <c r="B147" s="41"/>
+      <c r="C147" s="42"/>
     </row>
     <row r="148" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B148" s="54"/>
-      <c r="C148" s="55"/>
+      <c r="B148" s="41"/>
+      <c r="C148" s="42"/>
     </row>
     <row r="149" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B149" s="54"/>
-      <c r="C149" s="55"/>
+      <c r="B149" s="41"/>
+      <c r="C149" s="42"/>
     </row>
     <row r="150" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B150" s="54"/>
-      <c r="C150" s="55"/>
+      <c r="B150" s="41"/>
+      <c r="C150" s="42"/>
     </row>
     <row r="151" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B151" s="54"/>
-      <c r="C151" s="55"/>
+      <c r="B151" s="41"/>
+      <c r="C151" s="42"/>
     </row>
     <row r="152" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B152" s="54"/>
-      <c r="C152" s="55"/>
+      <c r="B152" s="41"/>
+      <c r="C152" s="42"/>
     </row>
     <row r="153" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B153" s="54"/>
-      <c r="C153" s="55"/>
+      <c r="B153" s="41"/>
+      <c r="C153" s="42"/>
     </row>
     <row r="154" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B154" s="54"/>
-      <c r="C154" s="55"/>
+      <c r="B154" s="41"/>
+      <c r="C154" s="42"/>
     </row>
     <row r="155" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B155" s="54"/>
-      <c r="C155" s="55"/>
+      <c r="B155" s="41"/>
+      <c r="C155" s="42"/>
     </row>
     <row r="156" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B156" s="54"/>
-      <c r="C156" s="55"/>
+      <c r="B156" s="41"/>
+      <c r="C156" s="42"/>
     </row>
     <row r="157" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B157" s="54"/>
-      <c r="C157" s="55"/>
+      <c r="B157" s="41"/>
+      <c r="C157" s="42"/>
     </row>
     <row r="158" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B158" s="54"/>
-      <c r="C158" s="55"/>
+      <c r="B158" s="41"/>
+      <c r="C158" s="42"/>
     </row>
     <row r="159" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B159" s="54"/>
-      <c r="C159" s="55"/>
+      <c r="B159" s="41"/>
+      <c r="C159" s="42"/>
     </row>
     <row r="160" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B160" s="54"/>
-      <c r="C160" s="55"/>
+      <c r="B160" s="41"/>
+      <c r="C160" s="42"/>
     </row>
     <row r="161" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B161" s="54"/>
-      <c r="C161" s="55"/>
+      <c r="B161" s="41"/>
+      <c r="C161" s="42"/>
     </row>
     <row r="162" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B162" s="54"/>
-      <c r="C162" s="55"/>
+      <c r="B162" s="41"/>
+      <c r="C162" s="42"/>
     </row>
     <row r="163" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B163" s="54"/>
-      <c r="C163" s="55"/>
+      <c r="B163" s="41"/>
+      <c r="C163" s="42"/>
     </row>
     <row r="164" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B164" s="54"/>
-      <c r="C164" s="55"/>
+      <c r="B164" s="41"/>
+      <c r="C164" s="42"/>
     </row>
     <row r="165" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B165" s="54"/>
-      <c r="C165" s="55"/>
+      <c r="B165" s="41"/>
+      <c r="C165" s="42"/>
     </row>
     <row r="166" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B166" s="54"/>
-      <c r="C166" s="55"/>
+      <c r="B166" s="41"/>
+      <c r="C166" s="42"/>
     </row>
     <row r="167" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B167" s="54"/>
-      <c r="C167" s="55"/>
+      <c r="B167" s="41"/>
+      <c r="C167" s="42"/>
     </row>
     <row r="168" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B168" s="54"/>
-      <c r="C168" s="55"/>
+      <c r="B168" s="41"/>
+      <c r="C168" s="42"/>
     </row>
     <row r="169" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B169" s="54"/>
-      <c r="C169" s="55"/>
+      <c r="B169" s="41"/>
+      <c r="C169" s="42"/>
     </row>
     <row r="170" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B170" s="54"/>
-      <c r="C170" s="55"/>
+      <c r="B170" s="41"/>
+      <c r="C170" s="42"/>
     </row>
     <row r="171" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B171" s="54"/>
-      <c r="C171" s="55"/>
+      <c r="B171" s="41"/>
+      <c r="C171" s="42"/>
     </row>
     <row r="172" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B172" s="54"/>
-      <c r="C172" s="55"/>
+      <c r="B172" s="41"/>
+      <c r="C172" s="42"/>
     </row>
     <row r="173" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B173" s="54"/>
-      <c r="C173" s="55"/>
+      <c r="B173" s="41"/>
+      <c r="C173" s="42"/>
     </row>
     <row r="174" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B174" s="54"/>
-      <c r="C174" s="55"/>
+      <c r="B174" s="41"/>
+      <c r="C174" s="42"/>
     </row>
     <row r="175" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B175" s="54"/>
-      <c r="C175" s="55"/>
+      <c r="B175" s="41"/>
+      <c r="C175" s="42"/>
     </row>
     <row r="176" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B176" s="54"/>
-      <c r="C176" s="55"/>
+      <c r="B176" s="41"/>
+      <c r="C176" s="42"/>
     </row>
     <row r="177" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B177" s="54"/>
-      <c r="C177" s="55"/>
+      <c r="B177" s="41"/>
+      <c r="C177" s="42"/>
     </row>
     <row r="178" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B178" s="54"/>
-      <c r="C178" s="55"/>
+      <c r="B178" s="41"/>
+      <c r="C178" s="42"/>
     </row>
     <row r="179" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B179" s="54"/>
-      <c r="C179" s="55"/>
+      <c r="B179" s="41"/>
+      <c r="C179" s="42"/>
     </row>
     <row r="180" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B180" s="54"/>
-      <c r="C180" s="55"/>
+      <c r="B180" s="41"/>
+      <c r="C180" s="42"/>
     </row>
     <row r="181" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B181" s="54"/>
-      <c r="C181" s="55"/>
+      <c r="B181" s="41"/>
+      <c r="C181" s="42"/>
     </row>
     <row r="182" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B182" s="54"/>
-      <c r="C182" s="55"/>
+      <c r="B182" s="41"/>
+      <c r="C182" s="42"/>
     </row>
     <row r="183" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B183" s="54"/>
-      <c r="C183" s="55"/>
+      <c r="B183" s="41"/>
+      <c r="C183" s="42"/>
     </row>
     <row r="184" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B184" s="54"/>
-      <c r="C184" s="55"/>
+      <c r="B184" s="41"/>
+      <c r="C184" s="42"/>
     </row>
     <row r="185" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B185" s="54"/>
-      <c r="C185" s="55"/>
+      <c r="B185" s="41"/>
+      <c r="C185" s="42"/>
     </row>
     <row r="186" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B186" s="54"/>
-      <c r="C186" s="55"/>
+      <c r="B186" s="41"/>
+      <c r="C186" s="42"/>
     </row>
     <row r="187" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B187" s="54"/>
-      <c r="C187" s="55"/>
+      <c r="B187" s="41"/>
+      <c r="C187" s="42"/>
     </row>
     <row r="188" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B188" s="54"/>
-      <c r="C188" s="55"/>
+      <c r="B188" s="41"/>
+      <c r="C188" s="42"/>
     </row>
     <row r="189" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B189" s="54"/>
-      <c r="C189" s="55"/>
+      <c r="B189" s="41"/>
+      <c r="C189" s="42"/>
     </row>
     <row r="190" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B190" s="54"/>
-      <c r="C190" s="55"/>
+      <c r="B190" s="41"/>
+      <c r="C190" s="42"/>
     </row>
     <row r="191" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B191" s="54"/>
-      <c r="C191" s="55"/>
+      <c r="B191" s="41"/>
+      <c r="C191" s="42"/>
     </row>
     <row r="192" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B192" s="54"/>
-      <c r="C192" s="55"/>
+      <c r="B192" s="41"/>
+      <c r="C192" s="42"/>
     </row>
     <row r="193" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B193" s="54"/>
-      <c r="C193" s="55"/>
+      <c r="B193" s="41"/>
+      <c r="C193" s="42"/>
     </row>
     <row r="194" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B194" s="54"/>
-      <c r="C194" s="55"/>
+      <c r="B194" s="41"/>
+      <c r="C194" s="42"/>
     </row>
     <row r="195" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B195" s="54"/>
-      <c r="C195" s="55"/>
+      <c r="B195" s="41"/>
+      <c r="C195" s="42"/>
     </row>
     <row r="196" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B196" s="54"/>
-      <c r="C196" s="55"/>
+      <c r="B196" s="41"/>
+      <c r="C196" s="42"/>
     </row>
     <row r="197" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B197" s="54"/>
-      <c r="C197" s="55"/>
+      <c r="B197" s="41"/>
+      <c r="C197" s="42"/>
     </row>
     <row r="198" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B198" s="54"/>
-      <c r="C198" s="55"/>
+      <c r="B198" s="41"/>
+      <c r="C198" s="42"/>
     </row>
     <row r="199" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B199" s="54"/>
-      <c r="C199" s="55"/>
+      <c r="B199" s="41"/>
+      <c r="C199" s="42"/>
     </row>
     <row r="200" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B200" s="54"/>
-      <c r="C200" s="55"/>
+      <c r="B200" s="41"/>
+      <c r="C200" s="42"/>
     </row>
     <row r="201" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B201" s="54"/>
-      <c r="C201" s="55"/>
+      <c r="B201" s="41"/>
+      <c r="C201" s="42"/>
     </row>
     <row r="202" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B202" s="54"/>
-      <c r="C202" s="55"/>
+      <c r="B202" s="41"/>
+      <c r="C202" s="42"/>
     </row>
     <row r="203" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B203" s="54"/>
-      <c r="C203" s="55"/>
+      <c r="B203" s="41"/>
+      <c r="C203" s="42"/>
     </row>
     <row r="204" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B204" s="54"/>
-      <c r="C204" s="55"/>
+      <c r="B204" s="41"/>
+      <c r="C204" s="42"/>
     </row>
     <row r="205" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B205" s="54"/>
-      <c r="C205" s="55"/>
+      <c r="B205" s="41"/>
+      <c r="C205" s="42"/>
     </row>
     <row r="206" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B206" s="54"/>
-      <c r="C206" s="55"/>
+      <c r="B206" s="41"/>
+      <c r="C206" s="42"/>
     </row>
     <row r="207" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B207" s="54"/>
-      <c r="C207" s="55"/>
+      <c r="B207" s="41"/>
+      <c r="C207" s="42"/>
     </row>
     <row r="208" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B208" s="54"/>
-      <c r="C208" s="55"/>
+      <c r="B208" s="41"/>
+      <c r="C208" s="42"/>
     </row>
     <row r="209" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B209" s="54"/>
-      <c r="C209" s="55"/>
+      <c r="B209" s="41"/>
+      <c r="C209" s="42"/>
     </row>
     <row r="210" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B210" s="54"/>
-      <c r="C210" s="55"/>
+      <c r="B210" s="41"/>
+      <c r="C210" s="42"/>
     </row>
     <row r="211" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B211" s="54"/>
-      <c r="C211" s="55"/>
+      <c r="B211" s="41"/>
+      <c r="C211" s="42"/>
     </row>
     <row r="212" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B212" s="54"/>
-      <c r="C212" s="55"/>
+      <c r="B212" s="41"/>
+      <c r="C212" s="42"/>
     </row>
     <row r="213" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B213" s="54"/>
-      <c r="C213" s="55"/>
+      <c r="B213" s="41"/>
+      <c r="C213" s="42"/>
     </row>
     <row r="214" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B214" s="54"/>
-      <c r="C214" s="55"/>
+      <c r="B214" s="41"/>
+      <c r="C214" s="42"/>
     </row>
     <row r="215" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B215" s="54"/>
-      <c r="C215" s="55"/>
+      <c r="B215" s="41"/>
+      <c r="C215" s="42"/>
     </row>
     <row r="216" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B216" s="54"/>
-      <c r="C216" s="55"/>
+      <c r="B216" s="41"/>
+      <c r="C216" s="42"/>
     </row>
     <row r="217" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B217" s="54"/>
-      <c r="C217" s="55"/>
+      <c r="B217" s="41"/>
+      <c r="C217" s="42"/>
     </row>
     <row r="218" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B218" s="54"/>
-      <c r="C218" s="55"/>
+      <c r="B218" s="41"/>
+      <c r="C218" s="42"/>
     </row>
     <row r="219" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B219" s="54"/>
-      <c r="C219" s="55"/>
+      <c r="B219" s="41"/>
+      <c r="C219" s="42"/>
     </row>
     <row r="220" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B220" s="54"/>
-      <c r="C220" s="55"/>
+      <c r="B220" s="41"/>
+      <c r="C220" s="42"/>
     </row>
     <row r="221" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B221" s="54"/>
-      <c r="C221" s="55"/>
+      <c r="B221" s="41"/>
+      <c r="C221" s="42"/>
     </row>
     <row r="222" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B222" s="54"/>
-      <c r="C222" s="55"/>
+      <c r="B222" s="41"/>
+      <c r="C222" s="42"/>
     </row>
     <row r="223" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B223" s="54"/>
-      <c r="C223" s="55"/>
+      <c r="B223" s="41"/>
+      <c r="C223" s="42"/>
     </row>
     <row r="224" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B224" s="54"/>
-      <c r="C224" s="55"/>
+      <c r="B224" s="41"/>
+      <c r="C224" s="42"/>
     </row>
     <row r="225" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B225" s="54"/>
-      <c r="C225" s="55"/>
+      <c r="B225" s="41"/>
+      <c r="C225" s="42"/>
     </row>
     <row r="226" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B226" s="54"/>
-      <c r="C226" s="55"/>
+      <c r="B226" s="41"/>
+      <c r="C226" s="42"/>
     </row>
     <row r="227" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B227" s="54"/>
-      <c r="C227" s="55"/>
+      <c r="B227" s="41"/>
+      <c r="C227" s="42"/>
     </row>
     <row r="228" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B228" s="54"/>
-      <c r="C228" s="55"/>
+      <c r="B228" s="41"/>
+      <c r="C228" s="42"/>
     </row>
     <row r="229" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B229" s="54"/>
-      <c r="C229" s="55"/>
+      <c r="B229" s="41"/>
+      <c r="C229" s="42"/>
     </row>
     <row r="230" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B230" s="54"/>
-      <c r="C230" s="55"/>
+      <c r="B230" s="41"/>
+      <c r="C230" s="42"/>
     </row>
     <row r="231" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B231" s="54"/>
-      <c r="C231" s="55"/>
+      <c r="B231" s="41"/>
+      <c r="C231" s="42"/>
     </row>
     <row r="232" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B232" s="54"/>
-      <c r="C232" s="55"/>
+      <c r="B232" s="41"/>
+      <c r="C232" s="42"/>
     </row>
     <row r="233" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B233" s="54"/>
-      <c r="C233" s="55"/>
+      <c r="B233" s="41"/>
+      <c r="C233" s="42"/>
     </row>
     <row r="234" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B234" s="54"/>
-      <c r="C234" s="55"/>
+      <c r="B234" s="41"/>
+      <c r="C234" s="42"/>
     </row>
     <row r="235" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B235" s="54"/>
-      <c r="C235" s="55"/>
+      <c r="B235" s="41"/>
+      <c r="C235" s="42"/>
     </row>
     <row r="236" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B236" s="54"/>
-      <c r="C236" s="55"/>
+      <c r="B236" s="41"/>
+      <c r="C236" s="42"/>
     </row>
     <row r="237" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B237" s="54"/>
-      <c r="C237" s="55"/>
+      <c r="B237" s="41"/>
+      <c r="C237" s="42"/>
     </row>
     <row r="238" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B238" s="54"/>
-      <c r="C238" s="55"/>
+      <c r="B238" s="41"/>
+      <c r="C238" s="42"/>
     </row>
     <row r="239" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B239" s="54"/>
-      <c r="C239" s="55"/>
+      <c r="B239" s="41"/>
+      <c r="C239" s="42"/>
     </row>
     <row r="240" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B240" s="54"/>
-      <c r="C240" s="55"/>
+      <c r="B240" s="41"/>
+      <c r="C240" s="42"/>
     </row>
     <row r="241" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B241" s="54"/>
-      <c r="C241" s="55"/>
+      <c r="B241" s="41"/>
+      <c r="C241" s="42"/>
     </row>
     <row r="242" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B242" s="54"/>
-      <c r="C242" s="55"/>
+      <c r="B242" s="41"/>
+      <c r="C242" s="42"/>
     </row>
     <row r="243" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B243" s="54"/>
-      <c r="C243" s="55"/>
+      <c r="B243" s="41"/>
+      <c r="C243" s="42"/>
     </row>
     <row r="244" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B244" s="54"/>
-      <c r="C244" s="55"/>
+      <c r="B244" s="41"/>
+      <c r="C244" s="42"/>
     </row>
     <row r="245" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B245" s="54"/>
-      <c r="C245" s="55"/>
+      <c r="B245" s="41"/>
+      <c r="C245" s="42"/>
     </row>
     <row r="246" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B246" s="54"/>
-      <c r="C246" s="55"/>
+      <c r="B246" s="41"/>
+      <c r="C246" s="42"/>
     </row>
     <row r="247" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B247" s="54"/>
-      <c r="C247" s="55"/>
+      <c r="B247" s="41"/>
+      <c r="C247" s="42"/>
     </row>
     <row r="248" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B248" s="54"/>
-      <c r="C248" s="55"/>
+      <c r="B248" s="41"/>
+      <c r="C248" s="42"/>
     </row>
     <row r="249" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B249" s="54"/>
-      <c r="C249" s="55"/>
+      <c r="B249" s="41"/>
+      <c r="C249" s="42"/>
     </row>
     <row r="250" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B250" s="54"/>
-      <c r="C250" s="55"/>
+      <c r="B250" s="41"/>
+      <c r="C250" s="42"/>
     </row>
     <row r="251" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B251" s="54"/>
-      <c r="C251" s="55"/>
+      <c r="B251" s="41"/>
+      <c r="C251" s="42"/>
     </row>
     <row r="252" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B252" s="54"/>
-      <c r="C252" s="55"/>
+      <c r="B252" s="41"/>
+      <c r="C252" s="42"/>
     </row>
     <row r="253" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B253" s="54"/>
-      <c r="C253" s="55"/>
+      <c r="B253" s="41"/>
+      <c r="C253" s="42"/>
     </row>
     <row r="254" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B254" s="54"/>
-      <c r="C254" s="55"/>
+      <c r="B254" s="41"/>
+      <c r="C254" s="42"/>
     </row>
     <row r="255" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B255" s="54"/>
-      <c r="C255" s="55"/>
+      <c r="B255" s="41"/>
+      <c r="C255" s="42"/>
     </row>
     <row r="256" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B256" s="54"/>
-      <c r="C256" s="55"/>
+      <c r="B256" s="41"/>
+      <c r="C256" s="42"/>
     </row>
     <row r="257" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B257" s="54"/>
-      <c r="C257" s="55"/>
+      <c r="B257" s="41"/>
+      <c r="C257" s="42"/>
     </row>
     <row r="258" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B258" s="54"/>
-      <c r="C258" s="55"/>
+      <c r="B258" s="41"/>
+      <c r="C258" s="42"/>
     </row>
     <row r="259" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B259" s="54"/>
-      <c r="C259" s="55"/>
+      <c r="B259" s="41"/>
+      <c r="C259" s="42"/>
     </row>
     <row r="260" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B260" s="54"/>
-      <c r="C260" s="55"/>
+      <c r="B260" s="41"/>
+      <c r="C260" s="42"/>
     </row>
     <row r="261" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B261" s="54"/>
-      <c r="C261" s="55"/>
+      <c r="B261" s="41"/>
+      <c r="C261" s="42"/>
     </row>
     <row r="262" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B262" s="54"/>
-      <c r="C262" s="55"/>
+      <c r="B262" s="41"/>
+      <c r="C262" s="42"/>
     </row>
     <row r="263" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B263" s="54"/>
-      <c r="C263" s="55"/>
+      <c r="B263" s="41"/>
+      <c r="C263" s="42"/>
     </row>
     <row r="264" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B264" s="54"/>
-      <c r="C264" s="55"/>
+      <c r="B264" s="41"/>
+      <c r="C264" s="42"/>
     </row>
     <row r="265" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B265" s="54"/>
-      <c r="C265" s="55"/>
+      <c r="B265" s="41"/>
+      <c r="C265" s="42"/>
     </row>
     <row r="266" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B266" s="54"/>
-      <c r="C266" s="55"/>
+      <c r="B266" s="41"/>
+      <c r="C266" s="42"/>
     </row>
     <row r="267" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B267" s="54"/>
-      <c r="C267" s="55"/>
+      <c r="B267" s="41"/>
+      <c r="C267" s="42"/>
     </row>
     <row r="268" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B268" s="54"/>
-      <c r="C268" s="55"/>
+      <c r="B268" s="41"/>
+      <c r="C268" s="42"/>
     </row>
     <row r="269" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B269" s="54"/>
-      <c r="C269" s="55"/>
+      <c r="B269" s="41"/>
+      <c r="C269" s="42"/>
     </row>
     <row r="270" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B270" s="54"/>
-      <c r="C270" s="55"/>
+      <c r="B270" s="41"/>
+      <c r="C270" s="42"/>
     </row>
     <row r="271" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B271" s="54"/>
-      <c r="C271" s="55"/>
+      <c r="B271" s="41"/>
+      <c r="C271" s="42"/>
     </row>
     <row r="272" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B272" s="54"/>
-      <c r="C272" s="55"/>
+      <c r="B272" s="41"/>
+      <c r="C272" s="42"/>
     </row>
     <row r="273" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B273" s="54"/>
-      <c r="C273" s="55"/>
+      <c r="B273" s="41"/>
+      <c r="C273" s="42"/>
     </row>
     <row r="274" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B274" s="54"/>
-      <c r="C274" s="55"/>
+      <c r="B274" s="41"/>
+      <c r="C274" s="42"/>
     </row>
     <row r="275" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B275" s="54"/>
-      <c r="C275" s="55"/>
+      <c r="B275" s="41"/>
+      <c r="C275" s="42"/>
     </row>
     <row r="276" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B276" s="54"/>
-      <c r="C276" s="55"/>
+      <c r="B276" s="41"/>
+      <c r="C276" s="42"/>
     </row>
     <row r="277" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B277" s="54"/>
-      <c r="C277" s="55"/>
+      <c r="B277" s="41"/>
+      <c r="C277" s="42"/>
     </row>
     <row r="278" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B278" s="54"/>
-      <c r="C278" s="55"/>
+      <c r="B278" s="41"/>
+      <c r="C278" s="42"/>
     </row>
     <row r="279" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B279" s="54"/>
-      <c r="C279" s="55"/>
+      <c r="B279" s="41"/>
+      <c r="C279" s="42"/>
     </row>
     <row r="280" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B280" s="54"/>
-      <c r="C280" s="55"/>
+      <c r="B280" s="41"/>
+      <c r="C280" s="42"/>
     </row>
     <row r="281" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B281" s="54"/>
-      <c r="C281" s="55"/>
+      <c r="B281" s="41"/>
+      <c r="C281" s="42"/>
     </row>
     <row r="282" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B282" s="54"/>
-      <c r="C282" s="55"/>
+      <c r="B282" s="41"/>
+      <c r="C282" s="42"/>
     </row>
     <row r="283" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B283" s="54"/>
-      <c r="C283" s="55"/>
+      <c r="B283" s="41"/>
+      <c r="C283" s="42"/>
     </row>
     <row r="284" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B284" s="54"/>
-      <c r="C284" s="55"/>
+      <c r="B284" s="41"/>
+      <c r="C284" s="42"/>
     </row>
     <row r="285" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B285" s="54"/>
-      <c r="C285" s="55"/>
+      <c r="B285" s="41"/>
+      <c r="C285" s="42"/>
     </row>
     <row r="286" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B286" s="54"/>
-      <c r="C286" s="55"/>
+      <c r="B286" s="41"/>
+      <c r="C286" s="42"/>
     </row>
     <row r="287" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B287" s="54"/>
-      <c r="C287" s="55"/>
+      <c r="B287" s="41"/>
+      <c r="C287" s="42"/>
     </row>
     <row r="288" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B288" s="54"/>
-      <c r="C288" s="55"/>
+      <c r="B288" s="41"/>
+      <c r="C288" s="42"/>
     </row>
     <row r="289" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B289" s="54"/>
-      <c r="C289" s="55"/>
+      <c r="B289" s="41"/>
+      <c r="C289" s="42"/>
     </row>
     <row r="290" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B290" s="54"/>
-      <c r="C290" s="55"/>
+      <c r="B290" s="41"/>
+      <c r="C290" s="42"/>
     </row>
     <row r="291" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B291" s="54"/>
-      <c r="C291" s="55"/>
+      <c r="B291" s="41"/>
+      <c r="C291" s="42"/>
     </row>
     <row r="292" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B292" s="54"/>
-      <c r="C292" s="55"/>
+      <c r="B292" s="41"/>
+      <c r="C292" s="42"/>
     </row>
     <row r="293" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B293" s="54"/>
-      <c r="C293" s="55"/>
+      <c r="B293" s="41"/>
+      <c r="C293" s="42"/>
     </row>
     <row r="294" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B294" s="54"/>
-      <c r="C294" s="55"/>
+      <c r="B294" s="41"/>
+      <c r="C294" s="42"/>
     </row>
     <row r="295" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B295" s="54"/>
-      <c r="C295" s="55"/>
+      <c r="B295" s="41"/>
+      <c r="C295" s="42"/>
     </row>
     <row r="296" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B296" s="54"/>
-      <c r="C296" s="55"/>
+      <c r="B296" s="41"/>
+      <c r="C296" s="42"/>
     </row>
     <row r="297" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B297" s="54"/>
-      <c r="C297" s="55"/>
+      <c r="B297" s="41"/>
+      <c r="C297" s="42"/>
     </row>
     <row r="298" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B298" s="54"/>
-      <c r="C298" s="55"/>
+      <c r="B298" s="41"/>
+      <c r="C298" s="42"/>
     </row>
     <row r="299" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B299" s="54"/>
-      <c r="C299" s="55"/>
+      <c r="B299" s="41"/>
+      <c r="C299" s="42"/>
     </row>
     <row r="300" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B300" s="54"/>
-      <c r="C300" s="55"/>
+      <c r="B300" s="41"/>
+      <c r="C300" s="42"/>
     </row>
     <row r="301" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B301" s="54"/>
-      <c r="C301" s="55"/>
+      <c r="B301" s="41"/>
+      <c r="C301" s="42"/>
     </row>
     <row r="302" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B302" s="54"/>
-      <c r="C302" s="55"/>
+      <c r="B302" s="41"/>
+      <c r="C302" s="42"/>
     </row>
     <row r="303" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B303" s="54"/>
-      <c r="C303" s="55"/>
+      <c r="B303" s="41"/>
+      <c r="C303" s="42"/>
     </row>
     <row r="304" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B304" s="54"/>
-      <c r="C304" s="55"/>
+      <c r="B304" s="41"/>
+      <c r="C304" s="42"/>
     </row>
     <row r="305" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B305" s="54"/>
-      <c r="C305" s="55"/>
+      <c r="B305" s="41"/>
+      <c r="C305" s="42"/>
     </row>
     <row r="306" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B306" s="54"/>
-      <c r="C306" s="55"/>
+      <c r="B306" s="41"/>
+      <c r="C306" s="42"/>
     </row>
     <row r="307" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B307" s="54"/>
-      <c r="C307" s="55"/>
+      <c r="B307" s="41"/>
+      <c r="C307" s="42"/>
     </row>
     <row r="308" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B308" s="54"/>
-      <c r="C308" s="55"/>
+      <c r="B308" s="41"/>
+      <c r="C308" s="42"/>
     </row>
     <row r="309" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B309" s="54"/>
-      <c r="C309" s="55"/>
+      <c r="B309" s="41"/>
+      <c r="C309" s="42"/>
     </row>
     <row r="310" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B310" s="54"/>
-      <c r="C310" s="55"/>
+      <c r="B310" s="41"/>
+      <c r="C310" s="42"/>
     </row>
     <row r="311" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B311" s="54"/>
-      <c r="C311" s="55"/>
+      <c r="B311" s="41"/>
+      <c r="C311" s="42"/>
     </row>
     <row r="312" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B312" s="54"/>
-      <c r="C312" s="55"/>
+      <c r="B312" s="41"/>
+      <c r="C312" s="42"/>
     </row>
     <row r="313" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B313" s="54"/>
-      <c r="C313" s="55"/>
+      <c r="B313" s="41"/>
+      <c r="C313" s="42"/>
     </row>
     <row r="314" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B314" s="54"/>
-      <c r="C314" s="55"/>
+      <c r="B314" s="41"/>
+      <c r="C314" s="42"/>
     </row>
     <row r="315" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B315" s="54"/>
-      <c r="C315" s="55"/>
+      <c r="B315" s="41"/>
+      <c r="C315" s="42"/>
     </row>
     <row r="316" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B316" s="54"/>
-      <c r="C316" s="55"/>
+      <c r="B316" s="41"/>
+      <c r="C316" s="42"/>
     </row>
     <row r="317" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B317" s="54"/>
-      <c r="C317" s="55"/>
+      <c r="B317" s="41"/>
+      <c r="C317" s="42"/>
     </row>
     <row r="318" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B318" s="54"/>
-      <c r="C318" s="55"/>
+      <c r="B318" s="41"/>
+      <c r="C318" s="42"/>
     </row>
     <row r="319" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B319" s="54"/>
-      <c r="C319" s="55"/>
+      <c r="B319" s="41"/>
+      <c r="C319" s="42"/>
     </row>
     <row r="320" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B320" s="54"/>
-      <c r="C320" s="55"/>
+      <c r="B320" s="41"/>
+      <c r="C320" s="42"/>
     </row>
     <row r="321" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B321" s="54"/>
-      <c r="C321" s="55"/>
+      <c r="B321" s="41"/>
+      <c r="C321" s="42"/>
     </row>
     <row r="322" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B322" s="54"/>
-      <c r="C322" s="55"/>
+      <c r="B322" s="41"/>
+      <c r="C322" s="42"/>
     </row>
     <row r="323" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B323" s="54"/>
-      <c r="C323" s="55"/>
+      <c r="B323" s="41"/>
+      <c r="C323" s="42"/>
     </row>
     <row r="324" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B324" s="54"/>
-      <c r="C324" s="55"/>
+      <c r="B324" s="41"/>
+      <c r="C324" s="42"/>
     </row>
     <row r="325" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B325" s="54"/>
-      <c r="C325" s="55"/>
+      <c r="B325" s="41"/>
+      <c r="C325" s="42"/>
     </row>
     <row r="326" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B326" s="54"/>
-      <c r="C326" s="55"/>
+      <c r="B326" s="41"/>
+      <c r="C326" s="42"/>
     </row>
     <row r="327" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B327" s="54"/>
-      <c r="C327" s="55"/>
+      <c r="B327" s="41"/>
+      <c r="C327" s="42"/>
     </row>
     <row r="328" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B328" s="54"/>
-      <c r="C328" s="55"/>
+      <c r="B328" s="41"/>
+      <c r="C328" s="42"/>
     </row>
     <row r="329" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B329" s="54"/>
-      <c r="C329" s="55"/>
+      <c r="B329" s="41"/>
+      <c r="C329" s="42"/>
     </row>
     <row r="330" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B330" s="54"/>
-      <c r="C330" s="55"/>
+      <c r="B330" s="41"/>
+      <c r="C330" s="42"/>
     </row>
     <row r="331" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B331" s="54"/>
-      <c r="C331" s="55"/>
+      <c r="B331" s="41"/>
+      <c r="C331" s="42"/>
     </row>
     <row r="332" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B332" s="54"/>
-      <c r="C332" s="55"/>
+      <c r="B332" s="41"/>
+      <c r="C332" s="42"/>
     </row>
     <row r="333" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B333" s="54"/>
-      <c r="C333" s="55"/>
+      <c r="B333" s="41"/>
+      <c r="C333" s="42"/>
     </row>
     <row r="334" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B334" s="54"/>
-      <c r="C334" s="55"/>
+      <c r="B334" s="41"/>
+      <c r="C334" s="42"/>
     </row>
     <row r="335" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B335" s="54"/>
-      <c r="C335" s="55"/>
+      <c r="B335" s="41"/>
+      <c r="C335" s="42"/>
     </row>
     <row r="336" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B336" s="54"/>
-      <c r="C336" s="55"/>
+      <c r="B336" s="41"/>
+      <c r="C336" s="42"/>
     </row>
     <row r="337" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B337" s="54"/>
-      <c r="C337" s="55"/>
+      <c r="B337" s="41"/>
+      <c r="C337" s="42"/>
     </row>
     <row r="338" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B338" s="54"/>
-      <c r="C338" s="55"/>
+      <c r="B338" s="41"/>
+      <c r="C338" s="42"/>
     </row>
     <row r="339" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B339" s="54"/>
-      <c r="C339" s="55"/>
+      <c r="B339" s="41"/>
+      <c r="C339" s="42"/>
     </row>
     <row r="340" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B340" s="54"/>
-      <c r="C340" s="55"/>
+      <c r="B340" s="41"/>
+      <c r="C340" s="42"/>
     </row>
     <row r="341" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B341" s="54"/>
-      <c r="C341" s="55"/>
+      <c r="B341" s="41"/>
+      <c r="C341" s="42"/>
     </row>
     <row r="342" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B342" s="54"/>
-      <c r="C342" s="55"/>
+      <c r="B342" s="41"/>
+      <c r="C342" s="42"/>
     </row>
     <row r="343" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B343" s="54"/>
-      <c r="C343" s="55"/>
+      <c r="B343" s="41"/>
+      <c r="C343" s="42"/>
     </row>
     <row r="344" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B344" s="54"/>
-      <c r="C344" s="55"/>
+      <c r="B344" s="41"/>
+      <c r="C344" s="42"/>
     </row>
     <row r="345" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B345" s="54"/>
-      <c r="C345" s="55"/>
+      <c r="B345" s="41"/>
+      <c r="C345" s="42"/>
     </row>
     <row r="346" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B346" s="54"/>
-      <c r="C346" s="55"/>
+      <c r="B346" s="41"/>
+      <c r="C346" s="42"/>
     </row>
     <row r="347" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B347" s="54"/>
-      <c r="C347" s="55"/>
+      <c r="B347" s="41"/>
+      <c r="C347" s="42"/>
     </row>
     <row r="348" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B348" s="54"/>
-      <c r="C348" s="55"/>
+      <c r="B348" s="41"/>
+      <c r="C348" s="42"/>
     </row>
     <row r="349" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B349" s="54"/>
-      <c r="C349" s="55"/>
+      <c r="B349" s="41"/>
+      <c r="C349" s="42"/>
     </row>
     <row r="350" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B350" s="54"/>
-      <c r="C350" s="55"/>
+      <c r="B350" s="41"/>
+      <c r="C350" s="42"/>
     </row>
     <row r="351" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B351" s="54"/>
-      <c r="C351" s="55"/>
+      <c r="B351" s="41"/>
+      <c r="C351" s="42"/>
     </row>
     <row r="352" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B352" s="54"/>
-      <c r="C352" s="55"/>
+      <c r="B352" s="41"/>
+      <c r="C352" s="42"/>
     </row>
     <row r="353" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B353" s="54"/>
-      <c r="C353" s="55"/>
+      <c r="B353" s="41"/>
+      <c r="C353" s="42"/>
     </row>
     <row r="354" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B354" s="54"/>
-      <c r="C354" s="55"/>
+      <c r="B354" s="41"/>
+      <c r="C354" s="42"/>
     </row>
     <row r="355" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B355" s="54"/>
-      <c r="C355" s="55"/>
+      <c r="B355" s="41"/>
+      <c r="C355" s="42"/>
     </row>
     <row r="356" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B356" s="54"/>
-      <c r="C356" s="55"/>
+      <c r="B356" s="41"/>
+      <c r="C356" s="42"/>
     </row>
     <row r="357" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B357" s="54"/>
-      <c r="C357" s="55"/>
+      <c r="B357" s="41"/>
+      <c r="C357" s="42"/>
     </row>
     <row r="358" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B358" s="54"/>
-      <c r="C358" s="55"/>
+      <c r="B358" s="41"/>
+      <c r="C358" s="42"/>
     </row>
     <row r="359" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B359" s="54"/>
-      <c r="C359" s="55"/>
+      <c r="B359" s="41"/>
+      <c r="C359" s="42"/>
     </row>
     <row r="360" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B360" s="54"/>
-      <c r="C360" s="55"/>
+      <c r="B360" s="41"/>
+      <c r="C360" s="42"/>
     </row>
     <row r="361" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B361" s="54"/>
-      <c r="C361" s="55"/>
+      <c r="B361" s="41"/>
+      <c r="C361" s="42"/>
     </row>
     <row r="362" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B362" s="54"/>
-      <c r="C362" s="55"/>
+      <c r="B362" s="41"/>
+      <c r="C362" s="42"/>
     </row>
     <row r="363" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B363" s="54"/>
-      <c r="C363" s="55"/>
+      <c r="B363" s="41"/>
+      <c r="C363" s="42"/>
     </row>
     <row r="364" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B364" s="54"/>
-      <c r="C364" s="55"/>
+      <c r="B364" s="41"/>
+      <c r="C364" s="42"/>
     </row>
     <row r="365" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B365" s="54"/>
-      <c r="C365" s="55"/>
+      <c r="B365" s="41"/>
+      <c r="C365" s="42"/>
     </row>
     <row r="366" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B366" s="54"/>
-      <c r="C366" s="55"/>
+      <c r="B366" s="41"/>
+      <c r="C366" s="42"/>
     </row>
     <row r="367" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B367" s="54"/>
-      <c r="C367" s="55"/>
+      <c r="B367" s="41"/>
+      <c r="C367" s="42"/>
     </row>
     <row r="368" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B368" s="54"/>
-      <c r="C368" s="55"/>
+      <c r="B368" s="41"/>
+      <c r="C368" s="42"/>
     </row>
     <row r="369" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B369" s="54"/>
-      <c r="C369" s="55"/>
+      <c r="B369" s="41"/>
+      <c r="C369" s="42"/>
     </row>
     <row r="370" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B370" s="54"/>
-      <c r="C370" s="55"/>
+      <c r="B370" s="41"/>
+      <c r="C370" s="42"/>
     </row>
     <row r="371" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B371" s="54"/>
-      <c r="C371" s="55"/>
+      <c r="B371" s="41"/>
+      <c r="C371" s="42"/>
     </row>
     <row r="372" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B372" s="54"/>
-      <c r="C372" s="55"/>
+      <c r="B372" s="41"/>
+      <c r="C372" s="42"/>
     </row>
     <row r="373" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B373" s="54"/>
-      <c r="C373" s="55"/>
+      <c r="B373" s="41"/>
+      <c r="C373" s="42"/>
     </row>
     <row r="374" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B374" s="54"/>
-      <c r="C374" s="55"/>
+      <c r="B374" s="41"/>
+      <c r="C374" s="42"/>
     </row>
     <row r="375" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B375" s="54"/>
-      <c r="C375" s="55"/>
+      <c r="B375" s="41"/>
+      <c r="C375" s="42"/>
     </row>
     <row r="376" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B376" s="54"/>
-      <c r="C376" s="55"/>
+      <c r="B376" s="41"/>
+      <c r="C376" s="42"/>
     </row>
     <row r="377" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B377" s="54"/>
-      <c r="C377" s="55"/>
+      <c r="B377" s="41"/>
+      <c r="C377" s="42"/>
     </row>
     <row r="378" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B378" s="54"/>
-      <c r="C378" s="55"/>
+      <c r="B378" s="41"/>
+      <c r="C378" s="42"/>
     </row>
     <row r="379" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B379" s="54"/>
-      <c r="C379" s="55"/>
+      <c r="B379" s="41"/>
+      <c r="C379" s="42"/>
     </row>
     <row r="380" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B380" s="54"/>
-      <c r="C380" s="55"/>
+      <c r="B380" s="41"/>
+      <c r="C380" s="42"/>
     </row>
     <row r="381" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B381" s="54"/>
-      <c r="C381" s="55"/>
+      <c r="B381" s="41"/>
+      <c r="C381" s="42"/>
     </row>
     <row r="382" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B382" s="54"/>
-      <c r="C382" s="55"/>
+      <c r="B382" s="41"/>
+      <c r="C382" s="42"/>
     </row>
     <row r="383" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B383" s="54"/>
-      <c r="C383" s="55"/>
+      <c r="B383" s="41"/>
+      <c r="C383" s="42"/>
     </row>
     <row r="384" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B384" s="54"/>
-      <c r="C384" s="55"/>
+      <c r="B384" s="41"/>
+      <c r="C384" s="42"/>
     </row>
     <row r="385" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B385" s="54"/>
-      <c r="C385" s="55"/>
+      <c r="B385" s="41"/>
+      <c r="C385" s="42"/>
     </row>
     <row r="386" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B386" s="54"/>
-      <c r="C386" s="55"/>
+      <c r="B386" s="41"/>
+      <c r="C386" s="42"/>
     </row>
     <row r="387" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B387" s="54"/>
-      <c r="C387" s="55"/>
+      <c r="B387" s="41"/>
+      <c r="C387" s="42"/>
     </row>
     <row r="388" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B388" s="54"/>
-      <c r="C388" s="55"/>
+      <c r="B388" s="41"/>
+      <c r="C388" s="42"/>
     </row>
     <row r="389" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B389" s="54"/>
-      <c r="C389" s="55"/>
+      <c r="B389" s="41"/>
+      <c r="C389" s="42"/>
     </row>
     <row r="390" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B390" s="54"/>
-      <c r="C390" s="55"/>
+      <c r="B390" s="41"/>
+      <c r="C390" s="42"/>
     </row>
     <row r="391" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B391" s="54"/>
-      <c r="C391" s="55"/>
+      <c r="B391" s="41"/>
+      <c r="C391" s="42"/>
     </row>
     <row r="392" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B392" s="54"/>
-      <c r="C392" s="55"/>
+      <c r="B392" s="41"/>
+      <c r="C392" s="42"/>
     </row>
     <row r="393" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B393" s="54"/>
-      <c r="C393" s="55"/>
+      <c r="B393" s="41"/>
+      <c r="C393" s="42"/>
     </row>
     <row r="394" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B394" s="54"/>
-      <c r="C394" s="55"/>
+      <c r="B394" s="41"/>
+      <c r="C394" s="42"/>
     </row>
     <row r="395" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B395" s="54"/>
-      <c r="C395" s="55"/>
+      <c r="B395" s="41"/>
+      <c r="C395" s="42"/>
     </row>
     <row r="396" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B396" s="54"/>
-      <c r="C396" s="55"/>
+      <c r="B396" s="41"/>
+      <c r="C396" s="42"/>
     </row>
     <row r="397" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B397" s="54"/>
-      <c r="C397" s="55"/>
+      <c r="B397" s="41"/>
+      <c r="C397" s="42"/>
     </row>
     <row r="398" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B398" s="54"/>
-      <c r="C398" s="55"/>
+      <c r="B398" s="41"/>
+      <c r="C398" s="42"/>
     </row>
     <row r="399" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B399" s="54"/>
-      <c r="C399" s="55"/>
+      <c r="B399" s="41"/>
+      <c r="C399" s="42"/>
     </row>
     <row r="400" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B400" s="54"/>
-      <c r="C400" s="55"/>
+      <c r="B400" s="41"/>
+      <c r="C400" s="42"/>
     </row>
     <row r="401" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B401" s="54"/>
-      <c r="C401" s="55"/>
+      <c r="B401" s="41"/>
+      <c r="C401" s="42"/>
     </row>
     <row r="402" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B402" s="54"/>
-      <c r="C402" s="55"/>
+      <c r="B402" s="41"/>
+      <c r="C402" s="42"/>
     </row>
     <row r="403" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B403" s="54"/>
-      <c r="C403" s="55"/>
+      <c r="B403" s="41"/>
+      <c r="C403" s="42"/>
     </row>
     <row r="404" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B404" s="54"/>
-      <c r="C404" s="55"/>
+      <c r="B404" s="41"/>
+      <c r="C404" s="42"/>
     </row>
     <row r="405" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B405" s="54"/>
-      <c r="C405" s="55"/>
+      <c r="B405" s="41"/>
+      <c r="C405" s="42"/>
     </row>
     <row r="406" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B406" s="54"/>
-      <c r="C406" s="55"/>
+      <c r="B406" s="41"/>
+      <c r="C406" s="42"/>
     </row>
     <row r="407" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B407" s="54"/>
-      <c r="C407" s="55"/>
+      <c r="B407" s="41"/>
+      <c r="C407" s="42"/>
     </row>
     <row r="408" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B408" s="54"/>
-      <c r="C408" s="55"/>
+      <c r="B408" s="41"/>
+      <c r="C408" s="42"/>
     </row>
     <row r="409" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B409" s="54"/>
-      <c r="C409" s="55"/>
+      <c r="B409" s="41"/>
+      <c r="C409" s="42"/>
     </row>
     <row r="410" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B410" s="54"/>
-      <c r="C410" s="55"/>
+      <c r="B410" s="41"/>
+      <c r="C410" s="42"/>
     </row>
     <row r="411" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B411" s="54"/>
-      <c r="C411" s="55"/>
+      <c r="B411" s="41"/>
+      <c r="C411" s="42"/>
     </row>
     <row r="412" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B412" s="54"/>
-      <c r="C412" s="55"/>
+      <c r="B412" s="41"/>
+      <c r="C412" s="42"/>
     </row>
     <row r="413" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B413" s="54"/>
-      <c r="C413" s="55"/>
+      <c r="B413" s="41"/>
+      <c r="C413" s="42"/>
     </row>
     <row r="414" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B414" s="54"/>
-      <c r="C414" s="55"/>
+      <c r="B414" s="41"/>
+      <c r="C414" s="42"/>
     </row>
     <row r="415" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B415" s="54"/>
-      <c r="C415" s="55"/>
+      <c r="B415" s="41"/>
+      <c r="C415" s="42"/>
     </row>
     <row r="416" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B416" s="54"/>
-      <c r="C416" s="55"/>
+      <c r="B416" s="41"/>
+      <c r="C416" s="42"/>
     </row>
     <row r="417" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B417" s="54"/>
-      <c r="C417" s="55"/>
+      <c r="B417" s="41"/>
+      <c r="C417" s="42"/>
     </row>
     <row r="418" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B418" s="54"/>
-      <c r="C418" s="55"/>
+      <c r="B418" s="41"/>
+      <c r="C418" s="42"/>
     </row>
     <row r="419" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B419" s="54"/>
-      <c r="C419" s="55"/>
+      <c r="B419" s="41"/>
+      <c r="C419" s="42"/>
     </row>
     <row r="420" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B420" s="54"/>
-      <c r="C420" s="55"/>
+      <c r="B420" s="41"/>
+      <c r="C420" s="42"/>
     </row>
     <row r="421" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B421" s="54"/>
-      <c r="C421" s="55"/>
+      <c r="B421" s="41"/>
+      <c r="C421" s="42"/>
     </row>
     <row r="422" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B422" s="54"/>
-      <c r="C422" s="55"/>
+      <c r="B422" s="41"/>
+      <c r="C422" s="42"/>
     </row>
     <row r="423" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B423" s="54"/>
-      <c r="C423" s="55"/>
+      <c r="B423" s="41"/>
+      <c r="C423" s="42"/>
     </row>
     <row r="424" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B424" s="54"/>
-      <c r="C424" s="55"/>
+      <c r="B424" s="41"/>
+      <c r="C424" s="42"/>
     </row>
     <row r="425" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B425" s="54"/>
-      <c r="C425" s="55"/>
+      <c r="B425" s="41"/>
+      <c r="C425" s="42"/>
     </row>
     <row r="426" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B426" s="54"/>
-      <c r="C426" s="55"/>
+      <c r="B426" s="41"/>
+      <c r="C426" s="42"/>
     </row>
     <row r="427" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B427" s="54"/>
-      <c r="C427" s="55"/>
+      <c r="B427" s="41"/>
+      <c r="C427" s="42"/>
     </row>
     <row r="428" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B428" s="54"/>
-      <c r="C428" s="55"/>
+      <c r="B428" s="41"/>
+      <c r="C428" s="42"/>
     </row>
     <row r="429" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B429" s="54"/>
-      <c r="C429" s="55"/>
+      <c r="B429" s="41"/>
+      <c r="C429" s="42"/>
     </row>
     <row r="430" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B430" s="54"/>
-      <c r="C430" s="55"/>
+      <c r="B430" s="41"/>
+      <c r="C430" s="42"/>
     </row>
     <row r="431" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B431" s="54"/>
-      <c r="C431" s="55"/>
+      <c r="B431" s="41"/>
+      <c r="C431" s="42"/>
     </row>
     <row r="432" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B432" s="54"/>
-      <c r="C432" s="55"/>
+      <c r="B432" s="41"/>
+      <c r="C432" s="42"/>
     </row>
     <row r="433" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B433" s="54"/>
-      <c r="C433" s="55"/>
+      <c r="B433" s="41"/>
+      <c r="C433" s="42"/>
     </row>
     <row r="434" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B434" s="54"/>
-      <c r="C434" s="55"/>
+      <c r="B434" s="41"/>
+      <c r="C434" s="42"/>
     </row>
     <row r="435" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B435" s="54"/>
-      <c r="C435" s="55"/>
+      <c r="B435" s="41"/>
+      <c r="C435" s="42"/>
     </row>
     <row r="436" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B436" s="54"/>
-      <c r="C436" s="55"/>
+      <c r="B436" s="41"/>
+      <c r="C436" s="42"/>
     </row>
     <row r="437" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B437" s="54"/>
-      <c r="C437" s="55"/>
+      <c r="B437" s="41"/>
+      <c r="C437" s="42"/>
     </row>
     <row r="438" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B438" s="54"/>
-      <c r="C438" s="55"/>
+      <c r="B438" s="41"/>
+      <c r="C438" s="42"/>
     </row>
     <row r="439" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B439" s="54"/>
-      <c r="C439" s="55"/>
+      <c r="B439" s="41"/>
+      <c r="C439" s="42"/>
     </row>
     <row r="440" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B440" s="54"/>
-      <c r="C440" s="55"/>
+      <c r="B440" s="41"/>
+      <c r="C440" s="42"/>
     </row>
     <row r="441" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B441" s="54"/>
-      <c r="C441" s="55"/>
+      <c r="B441" s="41"/>
+      <c r="C441" s="42"/>
     </row>
     <row r="442" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B442" s="54"/>
-      <c r="C442" s="55"/>
+      <c r="B442" s="41"/>
+      <c r="C442" s="42"/>
     </row>
     <row r="443" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B443" s="54"/>
-      <c r="C443" s="55"/>
+      <c r="B443" s="41"/>
+      <c r="C443" s="42"/>
     </row>
     <row r="444" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B444" s="54"/>
-      <c r="C444" s="55"/>
+      <c r="B444" s="41"/>
+      <c r="C444" s="42"/>
     </row>
     <row r="445" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B445" s="54"/>
-      <c r="C445" s="55"/>
+      <c r="B445" s="41"/>
+      <c r="C445" s="42"/>
     </row>
     <row r="446" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B446" s="54"/>
-      <c r="C446" s="55"/>
+      <c r="B446" s="41"/>
+      <c r="C446" s="42"/>
     </row>
     <row r="447" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B447" s="54"/>
-      <c r="C447" s="55"/>
+      <c r="B447" s="41"/>
+      <c r="C447" s="42"/>
     </row>
     <row r="448" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B448" s="54"/>
-      <c r="C448" s="55"/>
+      <c r="B448" s="41"/>
+      <c r="C448" s="42"/>
     </row>
     <row r="449" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B449" s="54"/>
-      <c r="C449" s="55"/>
+      <c r="B449" s="41"/>
+      <c r="C449" s="42"/>
     </row>
     <row r="450" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B450" s="54"/>
-      <c r="C450" s="55"/>
+      <c r="B450" s="41"/>
+      <c r="C450" s="42"/>
     </row>
     <row r="451" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B451" s="54"/>
-      <c r="C451" s="55"/>
+      <c r="B451" s="41"/>
+      <c r="C451" s="42"/>
     </row>
     <row r="452" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B452" s="54"/>
-      <c r="C452" s="55"/>
+      <c r="B452" s="41"/>
+      <c r="C452" s="42"/>
     </row>
     <row r="453" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B453" s="54"/>
-      <c r="C453" s="55"/>
+      <c r="B453" s="41"/>
+      <c r="C453" s="42"/>
     </row>
     <row r="454" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B454" s="54"/>
-      <c r="C454" s="55"/>
+      <c r="B454" s="41"/>
+      <c r="C454" s="42"/>
     </row>
     <row r="455" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B455" s="54"/>
-      <c r="C455" s="55"/>
+      <c r="B455" s="41"/>
+      <c r="C455" s="42"/>
     </row>
     <row r="456" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B456" s="54"/>
-      <c r="C456" s="55"/>
+      <c r="B456" s="41"/>
+      <c r="C456" s="42"/>
     </row>
     <row r="457" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B457" s="54"/>
-      <c r="C457" s="55"/>
+      <c r="B457" s="41"/>
+      <c r="C457" s="42"/>
     </row>
     <row r="458" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B458" s="54"/>
-      <c r="C458" s="55"/>
+      <c r="B458" s="41"/>
+      <c r="C458" s="42"/>
     </row>
     <row r="459" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B459" s="54"/>
-      <c r="C459" s="55"/>
+      <c r="B459" s="41"/>
+      <c r="C459" s="42"/>
     </row>
     <row r="460" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B460" s="54"/>
-      <c r="C460" s="55"/>
+      <c r="B460" s="41"/>
+      <c r="C460" s="42"/>
     </row>
     <row r="461" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B461" s="54"/>
-      <c r="C461" s="55"/>
+      <c r="B461" s="41"/>
+      <c r="C461" s="42"/>
     </row>
     <row r="462" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B462" s="54"/>
-      <c r="C462" s="55"/>
+      <c r="B462" s="41"/>
+      <c r="C462" s="42"/>
     </row>
     <row r="463" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B463" s="54"/>
-      <c r="C463" s="55"/>
+      <c r="B463" s="41"/>
+      <c r="C463" s="42"/>
     </row>
     <row r="464" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B464" s="54"/>
-      <c r="C464" s="55"/>
+      <c r="B464" s="41"/>
+      <c r="C464" s="42"/>
     </row>
     <row r="465" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B465" s="54"/>
-      <c r="C465" s="55"/>
+      <c r="B465" s="41"/>
+      <c r="C465" s="42"/>
     </row>
     <row r="466" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B466" s="54"/>
-      <c r="C466" s="55"/>
+      <c r="B466" s="41"/>
+      <c r="C466" s="42"/>
     </row>
     <row r="467" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B467" s="54"/>
-      <c r="C467" s="55"/>
+      <c r="B467" s="41"/>
+      <c r="C467" s="42"/>
     </row>
     <row r="468" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B468" s="54"/>
-      <c r="C468" s="55"/>
+      <c r="B468" s="41"/>
+      <c r="C468" s="42"/>
     </row>
     <row r="469" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B469" s="54"/>
-      <c r="C469" s="55"/>
+      <c r="B469" s="41"/>
+      <c r="C469" s="42"/>
     </row>
     <row r="470" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B470" s="54"/>
-      <c r="C470" s="55"/>
+      <c r="B470" s="41"/>
+      <c r="C470" s="42"/>
     </row>
     <row r="471" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B471" s="54"/>
-      <c r="C471" s="55"/>
+      <c r="B471" s="41"/>
+      <c r="C471" s="42"/>
     </row>
     <row r="472" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B472" s="54"/>
-      <c r="C472" s="55"/>
+      <c r="B472" s="41"/>
+      <c r="C472" s="42"/>
     </row>
     <row r="473" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B473" s="54"/>
-      <c r="C473" s="55"/>
+      <c r="B473" s="41"/>
+      <c r="C473" s="42"/>
     </row>
     <row r="474" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B474" s="54"/>
-      <c r="C474" s="55"/>
+      <c r="B474" s="41"/>
+      <c r="C474" s="42"/>
     </row>
     <row r="475" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B475" s="54"/>
-      <c r="C475" s="55"/>
+      <c r="B475" s="41"/>
+      <c r="C475" s="42"/>
     </row>
     <row r="476" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B476" s="54"/>
-      <c r="C476" s="55"/>
+      <c r="B476" s="41"/>
+      <c r="C476" s="42"/>
     </row>
     <row r="477" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B477" s="54"/>
-      <c r="C477" s="55"/>
+      <c r="B477" s="41"/>
+      <c r="C477" s="42"/>
     </row>
     <row r="478" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B478" s="54"/>
-      <c r="C478" s="55"/>
+      <c r="B478" s="41"/>
+      <c r="C478" s="42"/>
     </row>
     <row r="479" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B479" s="54"/>
-      <c r="C479" s="55"/>
+      <c r="B479" s="41"/>
+      <c r="C479" s="42"/>
     </row>
     <row r="480" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B480" s="54"/>
-      <c r="C480" s="55"/>
+      <c r="B480" s="41"/>
+      <c r="C480" s="42"/>
     </row>
     <row r="481" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B481" s="54"/>
-      <c r="C481" s="55"/>
+      <c r="B481" s="41"/>
+      <c r="C481" s="42"/>
     </row>
     <row r="482" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B482" s="54"/>
-      <c r="C482" s="55"/>
+      <c r="B482" s="41"/>
+      <c r="C482" s="42"/>
     </row>
     <row r="483" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B483" s="54"/>
-      <c r="C483" s="55"/>
+      <c r="B483" s="41"/>
+      <c r="C483" s="42"/>
     </row>
     <row r="484" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B484" s="54"/>
-      <c r="C484" s="55"/>
+      <c r="B484" s="41"/>
+      <c r="C484" s="42"/>
     </row>
     <row r="485" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B485" s="54"/>
-      <c r="C485" s="55"/>
+      <c r="B485" s="41"/>
+      <c r="C485" s="42"/>
     </row>
     <row r="486" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B486" s="54"/>
-      <c r="C486" s="55"/>
+      <c r="B486" s="41"/>
+      <c r="C486" s="42"/>
     </row>
     <row r="487" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B487" s="54"/>
-      <c r="C487" s="55"/>
+      <c r="B487" s="41"/>
+      <c r="C487" s="42"/>
     </row>
     <row r="488" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B488" s="54"/>
-      <c r="C488" s="55"/>
+      <c r="B488" s="41"/>
+      <c r="C488" s="42"/>
     </row>
     <row r="489" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B489" s="54"/>
-      <c r="C489" s="55"/>
+      <c r="B489" s="41"/>
+      <c r="C489" s="42"/>
     </row>
     <row r="490" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B490" s="54"/>
-      <c r="C490" s="55"/>
+      <c r="B490" s="41"/>
+      <c r="C490" s="42"/>
     </row>
     <row r="491" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B491" s="54"/>
-      <c r="C491" s="55"/>
+      <c r="B491" s="41"/>
+      <c r="C491" s="42"/>
     </row>
     <row r="492" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B492" s="54"/>
-      <c r="C492" s="55"/>
+      <c r="B492" s="41"/>
+      <c r="C492" s="42"/>
     </row>
     <row r="493" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B493" s="54"/>
-      <c r="C493" s="55"/>
+      <c r="B493" s="41"/>
+      <c r="C493" s="42"/>
     </row>
     <row r="494" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B494" s="54"/>
-      <c r="C494" s="55"/>
+      <c r="B494" s="41"/>
+      <c r="C494" s="42"/>
     </row>
     <row r="495" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B495" s="54"/>
-      <c r="C495" s="55"/>
+      <c r="B495" s="41"/>
+      <c r="C495" s="42"/>
     </row>
     <row r="496" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B496" s="54"/>
-      <c r="C496" s="55"/>
+      <c r="B496" s="41"/>
+      <c r="C496" s="42"/>
     </row>
     <row r="497" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B497" s="54"/>
-      <c r="C497" s="55"/>
+      <c r="B497" s="41"/>
+      <c r="C497" s="42"/>
     </row>
     <row r="498" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B498" s="54"/>
-      <c r="C498" s="55"/>
+      <c r="B498" s="41"/>
+      <c r="C498" s="42"/>
     </row>
     <row r="499" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B499" s="54"/>
-      <c r="C499" s="55"/>
+      <c r="B499" s="41"/>
+      <c r="C499" s="42"/>
     </row>
     <row r="500" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B500" s="54"/>
-      <c r="C500" s="55"/>
+      <c r="B500" s="41"/>
+      <c r="C500" s="42"/>
     </row>
     <row r="501" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B501" s="54"/>
-      <c r="C501" s="55"/>
+      <c r="B501" s="41"/>
+      <c r="C501" s="42"/>
     </row>
     <row r="502" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B502" s="54"/>
-      <c r="C502" s="55"/>
+      <c r="B502" s="41"/>
+      <c r="C502" s="42"/>
     </row>
     <row r="503" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B503" s="54"/>
-      <c r="C503" s="55"/>
+      <c r="B503" s="41"/>
+      <c r="C503" s="42"/>
     </row>
     <row r="504" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B504" s="54"/>
-      <c r="C504" s="55"/>
+      <c r="B504" s="41"/>
+      <c r="C504" s="42"/>
     </row>
     <row r="505" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B505" s="54"/>
-      <c r="C505" s="55"/>
+      <c r="B505" s="41"/>
+      <c r="C505" s="42"/>
     </row>
     <row r="506" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B506" s="54"/>
-      <c r="C506" s="55"/>
+      <c r="B506" s="41"/>
+      <c r="C506" s="42"/>
     </row>
     <row r="507" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B507" s="54"/>
-      <c r="C507" s="55"/>
+      <c r="B507" s="41"/>
+      <c r="C507" s="42"/>
     </row>
     <row r="508" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B508" s="54"/>
-      <c r="C508" s="55"/>
+      <c r="B508" s="41"/>
+      <c r="C508" s="42"/>
     </row>
     <row r="509" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B509" s="54"/>
-      <c r="C509" s="55"/>
+      <c r="B509" s="41"/>
+      <c r="C509" s="42"/>
     </row>
     <row r="510" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B510" s="54"/>
-      <c r="C510" s="55"/>
+      <c r="B510" s="41"/>
+      <c r="C510" s="42"/>
     </row>
     <row r="511" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B511" s="54"/>
-      <c r="C511" s="55"/>
+      <c r="B511" s="41"/>
+      <c r="C511" s="42"/>
     </row>
     <row r="512" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B512" s="54"/>
-      <c r="C512" s="55"/>
+      <c r="B512" s="41"/>
+      <c r="C512" s="42"/>
     </row>
     <row r="513" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B513" s="54"/>
-      <c r="C513" s="55"/>
+      <c r="B513" s="41"/>
+      <c r="C513" s="42"/>
     </row>
     <row r="514" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B514" s="54"/>
-      <c r="C514" s="55"/>
+      <c r="B514" s="41"/>
+      <c r="C514" s="42"/>
     </row>
     <row r="515" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B515" s="54"/>
-      <c r="C515" s="55"/>
+      <c r="B515" s="41"/>
+      <c r="C515" s="42"/>
     </row>
     <row r="516" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B516" s="54"/>
-      <c r="C516" s="55"/>
+      <c r="B516" s="41"/>
+      <c r="C516" s="42"/>
     </row>
     <row r="517" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B517" s="54"/>
-      <c r="C517" s="55"/>
+      <c r="B517" s="41"/>
+      <c r="C517" s="42"/>
     </row>
     <row r="518" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B518" s="54"/>
-      <c r="C518" s="55"/>
+      <c r="B518" s="41"/>
+      <c r="C518" s="42"/>
     </row>
     <row r="519" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B519" s="54"/>
-      <c r="C519" s="55"/>
+      <c r="B519" s="41"/>
+      <c r="C519" s="42"/>
     </row>
     <row r="520" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B520" s="54"/>
-      <c r="C520" s="55"/>
+      <c r="B520" s="41"/>
+      <c r="C520" s="42"/>
     </row>
     <row r="521" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B521" s="54"/>
-      <c r="C521" s="55"/>
+      <c r="B521" s="41"/>
+      <c r="C521" s="42"/>
     </row>
     <row r="522" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B522" s="54"/>
-      <c r="C522" s="55"/>
+      <c r="B522" s="41"/>
+      <c r="C522" s="42"/>
     </row>
     <row r="523" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B523" s="54"/>
-      <c r="C523" s="55"/>
+      <c r="B523" s="41"/>
+      <c r="C523" s="42"/>
     </row>
     <row r="524" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B524" s="54"/>
-      <c r="C524" s="55"/>
+      <c r="B524" s="41"/>
+      <c r="C524" s="42"/>
     </row>
     <row r="525" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B525" s="54"/>
-      <c r="C525" s="55"/>
+      <c r="B525" s="41"/>
+      <c r="C525" s="42"/>
     </row>
     <row r="526" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B526" s="54"/>
-      <c r="C526" s="55"/>
+      <c r="B526" s="41"/>
+      <c r="C526" s="42"/>
     </row>
     <row r="527" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B527" s="54"/>
-      <c r="C527" s="55"/>
+      <c r="B527" s="41"/>
+      <c r="C527" s="42"/>
     </row>
     <row r="528" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B528" s="54"/>
-      <c r="C528" s="55"/>
+      <c r="B528" s="41"/>
+      <c r="C528" s="42"/>
     </row>
     <row r="529" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B529" s="54"/>
-      <c r="C529" s="55"/>
+      <c r="B529" s="41"/>
+      <c r="C529" s="42"/>
     </row>
     <row r="530" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B530" s="54"/>
-      <c r="C530" s="55"/>
+      <c r="B530" s="41"/>
+      <c r="C530" s="42"/>
     </row>
     <row r="531" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B531" s="54"/>
-      <c r="C531" s="55"/>
+      <c r="B531" s="41"/>
+      <c r="C531" s="42"/>
     </row>
     <row r="532" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B532" s="54"/>
-      <c r="C532" s="55"/>
+      <c r="B532" s="41"/>
+      <c r="C532" s="42"/>
     </row>
     <row r="533" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B533" s="54"/>
-      <c r="C533" s="55"/>
+      <c r="B533" s="41"/>
+      <c r="C533" s="42"/>
     </row>
     <row r="534" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B534" s="54"/>
-      <c r="C534" s="55"/>
+      <c r="B534" s="41"/>
+      <c r="C534" s="42"/>
     </row>
     <row r="535" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B535" s="54"/>
-      <c r="C535" s="55"/>
+      <c r="B535" s="41"/>
+      <c r="C535" s="42"/>
     </row>
     <row r="536" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B536" s="54"/>
-      <c r="C536" s="55"/>
+      <c r="B536" s="41"/>
+      <c r="C536" s="42"/>
     </row>
     <row r="537" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B537" s="54"/>
-      <c r="C537" s="55"/>
+      <c r="B537" s="41"/>
+      <c r="C537" s="42"/>
     </row>
     <row r="538" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B538" s="54"/>
-      <c r="C538" s="55"/>
+      <c r="B538" s="41"/>
+      <c r="C538" s="42"/>
     </row>
     <row r="539" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B539" s="54"/>
-      <c r="C539" s="55"/>
+      <c r="B539" s="41"/>
+      <c r="C539" s="42"/>
     </row>
     <row r="540" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B540" s="54"/>
-      <c r="C540" s="55"/>
+      <c r="B540" s="41"/>
+      <c r="C540" s="42"/>
     </row>
     <row r="541" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B541" s="54"/>
-      <c r="C541" s="55"/>
+      <c r="B541" s="41"/>
+      <c r="C541" s="42"/>
     </row>
     <row r="542" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B542" s="54"/>
-      <c r="C542" s="55"/>
+      <c r="B542" s="41"/>
+      <c r="C542" s="42"/>
     </row>
     <row r="543" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B543" s="54"/>
-      <c r="C543" s="55"/>
+      <c r="B543" s="41"/>
+      <c r="C543" s="42"/>
     </row>
     <row r="544" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B544" s="54"/>
-      <c r="C544" s="55"/>
+      <c r="B544" s="41"/>
+      <c r="C544" s="42"/>
     </row>
     <row r="545" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B545" s="54"/>
-      <c r="C545" s="55"/>
+      <c r="B545" s="41"/>
+      <c r="C545" s="42"/>
     </row>
     <row r="546" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B546" s="54"/>
-      <c r="C546" s="55"/>
+      <c r="B546" s="41"/>
+      <c r="C546" s="42"/>
     </row>
     <row r="547" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B547" s="54"/>
-      <c r="C547" s="55"/>
+      <c r="B547" s="41"/>
+      <c r="C547" s="42"/>
     </row>
     <row r="548" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B548" s="54"/>
-      <c r="C548" s="55"/>
+      <c r="B548" s="41"/>
+      <c r="C548" s="42"/>
     </row>
     <row r="549" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B549" s="54"/>
-      <c r="C549" s="55"/>
+      <c r="B549" s="41"/>
+      <c r="C549" s="42"/>
     </row>
     <row r="550" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B550" s="54"/>
-      <c r="C550" s="55"/>
+      <c r="B550" s="41"/>
+      <c r="C550" s="42"/>
     </row>
     <row r="551" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B551" s="54"/>
-      <c r="C551" s="55"/>
+      <c r="B551" s="41"/>
+      <c r="C551" s="42"/>
     </row>
     <row r="552" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B552" s="54"/>
-      <c r="C552" s="55"/>
+      <c r="B552" s="41"/>
+      <c r="C552" s="42"/>
     </row>
     <row r="553" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B553" s="54"/>
-      <c r="C553" s="55"/>
+      <c r="B553" s="41"/>
+      <c r="C553" s="42"/>
     </row>
     <row r="554" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B554" s="54"/>
-      <c r="C554" s="55"/>
+      <c r="B554" s="41"/>
+      <c r="C554" s="42"/>
     </row>
     <row r="555" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B555" s="54"/>
-      <c r="C555" s="55"/>
+      <c r="B555" s="41"/>
+      <c r="C555" s="42"/>
     </row>
     <row r="556" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B556" s="54"/>
-      <c r="C556" s="55"/>
+      <c r="B556" s="41"/>
+      <c r="C556" s="42"/>
     </row>
     <row r="557" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B557" s="54"/>
-      <c r="C557" s="55"/>
+      <c r="B557" s="41"/>
+      <c r="C557" s="42"/>
     </row>
     <row r="558" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B558" s="54"/>
-      <c r="C558" s="55"/>
+      <c r="B558" s="41"/>
+      <c r="C558" s="42"/>
     </row>
     <row r="559" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B559" s="54"/>
-      <c r="C559" s="55"/>
+      <c r="B559" s="41"/>
+      <c r="C559" s="42"/>
     </row>
     <row r="560" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B560" s="54"/>
-      <c r="C560" s="55"/>
+      <c r="B560" s="41"/>
+      <c r="C560" s="42"/>
     </row>
     <row r="561" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B561" s="54"/>
-      <c r="C561" s="55"/>
+      <c r="B561" s="41"/>
+      <c r="C561" s="42"/>
     </row>
     <row r="562" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B562" s="54"/>
-      <c r="C562" s="55"/>
+      <c r="B562" s="41"/>
+      <c r="C562" s="42"/>
     </row>
     <row r="563" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B563" s="54"/>
-      <c r="C563" s="55"/>
+      <c r="B563" s="41"/>
+      <c r="C563" s="42"/>
     </row>
     <row r="564" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B564" s="54"/>
-      <c r="C564" s="55"/>
+      <c r="B564" s="41"/>
+      <c r="C564" s="42"/>
     </row>
     <row r="565" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B565" s="54"/>
-      <c r="C565" s="55"/>
+      <c r="B565" s="41"/>
+      <c r="C565" s="42"/>
     </row>
     <row r="566" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B566" s="54"/>
-      <c r="C566" s="55"/>
+      <c r="B566" s="41"/>
+      <c r="C566" s="42"/>
     </row>
     <row r="567" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B567" s="54"/>
-      <c r="C567" s="55"/>
+      <c r="B567" s="41"/>
+      <c r="C567" s="42"/>
     </row>
     <row r="568" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B568" s="54"/>
-      <c r="C568" s="55"/>
+      <c r="B568" s="41"/>
+      <c r="C568" s="42"/>
     </row>
     <row r="569" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B569" s="54"/>
-      <c r="C569" s="55"/>
+      <c r="B569" s="41"/>
+      <c r="C569" s="42"/>
     </row>
     <row r="570" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B570" s="54"/>
-      <c r="C570" s="55"/>
+      <c r="B570" s="41"/>
+      <c r="C570" s="42"/>
     </row>
     <row r="571" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B571" s="54"/>
-      <c r="C571" s="55"/>
+      <c r="B571" s="41"/>
+      <c r="C571" s="42"/>
     </row>
     <row r="572" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B572" s="54"/>
-      <c r="C572" s="55"/>
+      <c r="B572" s="41"/>
+      <c r="C572" s="42"/>
     </row>
     <row r="573" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B573" s="54"/>
-      <c r="C573" s="55"/>
+      <c r="B573" s="41"/>
+      <c r="C573" s="42"/>
     </row>
     <row r="574" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B574" s="54"/>
-      <c r="C574" s="55"/>
+      <c r="B574" s="41"/>
+      <c r="C574" s="42"/>
     </row>
     <row r="575" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B575" s="54"/>
-      <c r="C575" s="55"/>
+      <c r="B575" s="41"/>
+      <c r="C575" s="42"/>
     </row>
     <row r="576" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B576" s="54"/>
-      <c r="C576" s="55"/>
+      <c r="B576" s="41"/>
+      <c r="C576" s="42"/>
     </row>
     <row r="577" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B577" s="54"/>
-      <c r="C577" s="55"/>
+      <c r="B577" s="41"/>
+      <c r="C577" s="42"/>
     </row>
     <row r="578" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B578" s="54"/>
-      <c r="C578" s="55"/>
+      <c r="B578" s="41"/>
+      <c r="C578" s="42"/>
     </row>
     <row r="579" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B579" s="54"/>
-      <c r="C579" s="55"/>
+      <c r="B579" s="41"/>
+      <c r="C579" s="42"/>
     </row>
     <row r="580" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B580" s="54"/>
-      <c r="C580" s="55"/>
+      <c r="B580" s="41"/>
+      <c r="C580" s="42"/>
     </row>
     <row r="581" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B581" s="54"/>
-      <c r="C581" s="55"/>
+      <c r="B581" s="41"/>
+      <c r="C581" s="42"/>
     </row>
     <row r="582" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B582" s="54"/>
-      <c r="C582" s="55"/>
+      <c r="B582" s="41"/>
+      <c r="C582" s="42"/>
     </row>
     <row r="583" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B583" s="54"/>
-      <c r="C583" s="55"/>
+      <c r="B583" s="41"/>
+      <c r="C583" s="42"/>
     </row>
     <row r="584" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B584" s="54"/>
-      <c r="C584" s="55"/>
+      <c r="B584" s="41"/>
+      <c r="C584" s="42"/>
     </row>
     <row r="585" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B585" s="54"/>
-      <c r="C585" s="55"/>
+      <c r="B585" s="41"/>
+      <c r="C585" s="42"/>
     </row>
     <row r="586" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B586" s="54"/>
-      <c r="C586" s="55"/>
+      <c r="B586" s="41"/>
+      <c r="C586" s="42"/>
     </row>
     <row r="587" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B587" s="54"/>
-      <c r="C587" s="55"/>
+      <c r="B587" s="41"/>
+      <c r="C587" s="42"/>
     </row>
     <row r="588" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B588" s="54"/>
-      <c r="C588" s="55"/>
+      <c r="B588" s="41"/>
+      <c r="C588" s="42"/>
     </row>
     <row r="589" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B589" s="54"/>
-      <c r="C589" s="55"/>
+      <c r="B589" s="41"/>
+      <c r="C589" s="42"/>
     </row>
     <row r="590" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B590" s="54"/>
-      <c r="C590" s="55"/>
+      <c r="B590" s="41"/>
+      <c r="C590" s="42"/>
     </row>
     <row r="591" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B591" s="54"/>
-      <c r="C591" s="55"/>
+      <c r="B591" s="41"/>
+      <c r="C591" s="42"/>
     </row>
     <row r="592" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B592" s="54"/>
-      <c r="C592" s="55"/>
+      <c r="B592" s="41"/>
+      <c r="C592" s="42"/>
     </row>
     <row r="593" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B593" s="54"/>
-      <c r="C593" s="55"/>
+      <c r="B593" s="41"/>
+      <c r="C593" s="42"/>
     </row>
     <row r="594" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B594" s="54"/>
-      <c r="C594" s="55"/>
+      <c r="B594" s="41"/>
+      <c r="C594" s="42"/>
     </row>
     <row r="595" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B595" s="54"/>
-      <c r="C595" s="55"/>
+      <c r="B595" s="41"/>
+      <c r="C595" s="42"/>
     </row>
     <row r="596" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B596" s="54"/>
-      <c r="C596" s="55"/>
+      <c r="B596" s="41"/>
+      <c r="C596" s="42"/>
     </row>
     <row r="597" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B597" s="54"/>
-      <c r="C597" s="55"/>
+      <c r="B597" s="41"/>
+      <c r="C597" s="42"/>
     </row>
     <row r="598" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B598" s="54"/>
-      <c r="C598" s="55"/>
+      <c r="B598" s="41"/>
+      <c r="C598" s="42"/>
     </row>
     <row r="599" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B599" s="54"/>
-      <c r="C599" s="55"/>
+      <c r="B599" s="41"/>
+      <c r="C599" s="42"/>
     </row>
     <row r="600" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B600" s="54"/>
-      <c r="C600" s="55"/>
+      <c r="B600" s="41"/>
+      <c r="C600" s="42"/>
     </row>
     <row r="601" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B601" s="54"/>
-      <c r="C601" s="55"/>
+      <c r="B601" s="41"/>
+      <c r="C601" s="42"/>
     </row>
     <row r="602" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B602" s="54"/>
-      <c r="C602" s="55"/>
+      <c r="B602" s="41"/>
+      <c r="C602" s="42"/>
     </row>
     <row r="603" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B603" s="54"/>
-      <c r="C603" s="55"/>
+      <c r="B603" s="41"/>
+      <c r="C603" s="42"/>
     </row>
     <row r="604" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B604" s="54"/>
-      <c r="C604" s="55"/>
+      <c r="B604" s="41"/>
+      <c r="C604" s="42"/>
     </row>
     <row r="605" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B605" s="54"/>
-      <c r="C605" s="55"/>
+      <c r="B605" s="41"/>
+      <c r="C605" s="42"/>
     </row>
     <row r="606" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B606" s="54"/>
-      <c r="C606" s="55"/>
+      <c r="B606" s="41"/>
+      <c r="C606" s="42"/>
     </row>
     <row r="607" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B607" s="54"/>
-      <c r="C607" s="55"/>
+      <c r="B607" s="41"/>
+      <c r="C607" s="42"/>
     </row>
     <row r="608" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B608" s="54"/>
-      <c r="C608" s="55"/>
+      <c r="B608" s="41"/>
+      <c r="C608" s="42"/>
     </row>
     <row r="609" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B609" s="54"/>
-      <c r="C609" s="55"/>
+      <c r="B609" s="41"/>
+      <c r="C609" s="42"/>
     </row>
     <row r="610" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B610" s="54"/>
-      <c r="C610" s="55"/>
+      <c r="B610" s="41"/>
+      <c r="C610" s="42"/>
     </row>
     <row r="611" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B611" s="54"/>
-      <c r="C611" s="55"/>
+      <c r="B611" s="41"/>
+      <c r="C611" s="42"/>
     </row>
     <row r="612" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B612" s="54"/>
-      <c r="C612" s="55"/>
+      <c r="B612" s="41"/>
+      <c r="C612" s="42"/>
     </row>
     <row r="613" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B613" s="54"/>
-      <c r="C613" s="55"/>
+      <c r="B613" s="41"/>
+      <c r="C613" s="42"/>
     </row>
     <row r="614" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B614" s="54"/>
-      <c r="C614" s="55"/>
+      <c r="B614" s="41"/>
+      <c r="C614" s="42"/>
     </row>
     <row r="615" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B615" s="54"/>
-      <c r="C615" s="55"/>
+      <c r="B615" s="41"/>
+      <c r="C615" s="42"/>
     </row>
     <row r="616" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B616" s="54"/>
-      <c r="C616" s="55"/>
+      <c r="B616" s="41"/>
+      <c r="C616" s="42"/>
     </row>
     <row r="617" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B617" s="54"/>
-      <c r="C617" s="55"/>
+      <c r="B617" s="41"/>
+      <c r="C617" s="42"/>
     </row>
     <row r="618" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B618" s="54"/>
-      <c r="C618" s="55"/>
+      <c r="B618" s="41"/>
+      <c r="C618" s="42"/>
     </row>
     <row r="619" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B619" s="54"/>
-      <c r="C619" s="55"/>
+      <c r="B619" s="41"/>
+      <c r="C619" s="42"/>
     </row>
     <row r="620" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B620" s="54"/>
-      <c r="C620" s="55"/>
+      <c r="B620" s="41"/>
+      <c r="C620" s="42"/>
     </row>
     <row r="621" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B621" s="54"/>
-      <c r="C621" s="55"/>
+      <c r="B621" s="41"/>
+      <c r="C621" s="42"/>
     </row>
     <row r="622" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B622" s="54"/>
-      <c r="C622" s="55"/>
+      <c r="B622" s="41"/>
+      <c r="C622" s="42"/>
     </row>
     <row r="623" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B623" s="54"/>
-      <c r="C623" s="55"/>
+      <c r="B623" s="41"/>
+      <c r="C623" s="42"/>
     </row>
     <row r="624" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B624" s="54"/>
-      <c r="C624" s="55"/>
+      <c r="B624" s="41"/>
+      <c r="C624" s="42"/>
     </row>
     <row r="625" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B625" s="54"/>
-      <c r="C625" s="55"/>
+      <c r="B625" s="41"/>
+      <c r="C625" s="42"/>
     </row>
     <row r="626" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B626" s="54"/>
-      <c r="C626" s="55"/>
+      <c r="B626" s="41"/>
+      <c r="C626" s="42"/>
     </row>
     <row r="627" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B627" s="54"/>
-      <c r="C627" s="55"/>
+      <c r="B627" s="41"/>
+      <c r="C627" s="42"/>
     </row>
     <row r="628" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B628" s="54"/>
-      <c r="C628" s="55"/>
+      <c r="B628" s="41"/>
+      <c r="C628" s="42"/>
     </row>
     <row r="629" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B629" s="54"/>
-      <c r="C629" s="55"/>
+      <c r="B629" s="41"/>
+      <c r="C629" s="42"/>
     </row>
     <row r="630" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B630" s="54"/>
-      <c r="C630" s="55"/>
+      <c r="B630" s="41"/>
+      <c r="C630" s="42"/>
     </row>
     <row r="631" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B631" s="54"/>
-      <c r="C631" s="55"/>
+      <c r="B631" s="41"/>
+      <c r="C631" s="42"/>
     </row>
     <row r="632" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B632" s="54"/>
-      <c r="C632" s="55"/>
+      <c r="B632" s="41"/>
+      <c r="C632" s="42"/>
     </row>
     <row r="633" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B633" s="54"/>
-      <c r="C633" s="55"/>
+      <c r="B633" s="41"/>
+      <c r="C633" s="42"/>
     </row>
     <row r="634" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B634" s="54"/>
-      <c r="C634" s="55"/>
+      <c r="B634" s="41"/>
+      <c r="C634" s="42"/>
     </row>
     <row r="635" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B635" s="54"/>
-      <c r="C635" s="55"/>
+      <c r="B635" s="41"/>
+      <c r="C635" s="42"/>
     </row>
     <row r="636" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B636" s="54"/>
-      <c r="C636" s="55"/>
+      <c r="B636" s="41"/>
+      <c r="C636" s="42"/>
     </row>
     <row r="637" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B637" s="54"/>
-      <c r="C637" s="55"/>
+      <c r="B637" s="41"/>
+      <c r="C637" s="42"/>
     </row>
     <row r="638" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B638" s="54"/>
-      <c r="C638" s="55"/>
+      <c r="B638" s="41"/>
+      <c r="C638" s="42"/>
     </row>
     <row r="639" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B639" s="54"/>
-      <c r="C639" s="55"/>
+      <c r="B639" s="41"/>
+      <c r="C639" s="42"/>
     </row>
     <row r="640" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B640" s="54"/>
-      <c r="C640" s="55"/>
+      <c r="B640" s="41"/>
+      <c r="C640" s="42"/>
     </row>
     <row r="641" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B641" s="54"/>
-      <c r="C641" s="55"/>
+      <c r="B641" s="41"/>
+      <c r="C641" s="42"/>
     </row>
     <row r="642" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B642" s="54"/>
-      <c r="C642" s="55"/>
+      <c r="B642" s="41"/>
+      <c r="C642" s="42"/>
     </row>
     <row r="643" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B643" s="54"/>
-      <c r="C643" s="55"/>
+      <c r="B643" s="41"/>
+      <c r="C643" s="42"/>
     </row>
     <row r="644" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B644" s="54"/>
-      <c r="C644" s="55"/>
+      <c r="B644" s="41"/>
+      <c r="C644" s="42"/>
     </row>
     <row r="645" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B645" s="54"/>
-      <c r="C645" s="55"/>
+      <c r="B645" s="41"/>
+      <c r="C645" s="42"/>
     </row>
     <row r="646" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B646" s="54"/>
-      <c r="C646" s="55"/>
+      <c r="B646" s="41"/>
+      <c r="C646" s="42"/>
     </row>
     <row r="647" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B647" s="54"/>
-      <c r="C647" s="55"/>
+      <c r="B647" s="41"/>
+      <c r="C647" s="42"/>
     </row>
     <row r="648" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B648" s="54"/>
-      <c r="C648" s="55"/>
+      <c r="B648" s="41"/>
+      <c r="C648" s="42"/>
     </row>
     <row r="649" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B649" s="54"/>
-      <c r="C649" s="55"/>
+      <c r="B649" s="41"/>
+      <c r="C649" s="42"/>
     </row>
     <row r="650" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B650" s="54"/>
-      <c r="C650" s="55"/>
+      <c r="B650" s="41"/>
+      <c r="C650" s="42"/>
     </row>
     <row r="651" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B651" s="54"/>
-      <c r="C651" s="55"/>
+      <c r="B651" s="41"/>
+      <c r="C651" s="42"/>
     </row>
     <row r="652" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B652" s="54"/>
-      <c r="C652" s="55"/>
+      <c r="B652" s="41"/>
+      <c r="C652" s="42"/>
     </row>
     <row r="653" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B653" s="54"/>
-      <c r="C653" s="55"/>
+      <c r="B653" s="41"/>
+      <c r="C653" s="42"/>
     </row>
     <row r="654" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B654" s="54"/>
-      <c r="C654" s="55"/>
+      <c r="B654" s="41"/>
+      <c r="C654" s="42"/>
     </row>
     <row r="655" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B655" s="54"/>
-      <c r="C655" s="55"/>
+      <c r="B655" s="41"/>
+      <c r="C655" s="42"/>
     </row>
     <row r="656" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B656" s="54"/>
-      <c r="C656" s="55"/>
+      <c r="B656" s="41"/>
+      <c r="C656" s="42"/>
     </row>
     <row r="657" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B657" s="54"/>
-      <c r="C657" s="55"/>
+      <c r="B657" s="41"/>
+      <c r="C657" s="42"/>
     </row>
     <row r="658" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B658" s="54"/>
-      <c r="C658" s="55"/>
+      <c r="B658" s="41"/>
+      <c r="C658" s="42"/>
     </row>
     <row r="659" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B659" s="54"/>
-      <c r="C659" s="55"/>
+      <c r="B659" s="41"/>
+      <c r="C659" s="42"/>
     </row>
     <row r="660" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B660" s="54"/>
-      <c r="C660" s="55"/>
+      <c r="B660" s="41"/>
+      <c r="C660" s="42"/>
     </row>
     <row r="661" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B661" s="54"/>
-      <c r="C661" s="55"/>
+      <c r="B661" s="41"/>
+      <c r="C661" s="42"/>
     </row>
     <row r="662" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B662" s="54"/>
-      <c r="C662" s="55"/>
+      <c r="B662" s="41"/>
+      <c r="C662" s="42"/>
     </row>
     <row r="663" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B663" s="54"/>
-      <c r="C663" s="55"/>
+      <c r="B663" s="41"/>
+      <c r="C663" s="42"/>
     </row>
     <row r="664" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B664" s="54"/>
-      <c r="C664" s="55"/>
+      <c r="B664" s="41"/>
+      <c r="C664" s="42"/>
     </row>
     <row r="665" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B665" s="54"/>
-      <c r="C665" s="55"/>
+      <c r="B665" s="41"/>
+      <c r="C665" s="42"/>
     </row>
     <row r="666" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B666" s="54"/>
-      <c r="C666" s="55"/>
+      <c r="B666" s="41"/>
+      <c r="C666" s="42"/>
     </row>
     <row r="667" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B667" s="54"/>
-      <c r="C667" s="55"/>
+      <c r="B667" s="41"/>
+      <c r="C667" s="42"/>
     </row>
     <row r="668" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B668" s="54"/>
-      <c r="C668" s="55"/>
+      <c r="B668" s="41"/>
+      <c r="C668" s="42"/>
     </row>
     <row r="669" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B669" s="54"/>
-      <c r="C669" s="55"/>
+      <c r="B669" s="41"/>
+      <c r="C669" s="42"/>
     </row>
     <row r="670" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B670" s="54"/>
-      <c r="C670" s="55"/>
+      <c r="B670" s="41"/>
+      <c r="C670" s="42"/>
     </row>
     <row r="671" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B671" s="54"/>
-      <c r="C671" s="55"/>
+      <c r="B671" s="41"/>
+      <c r="C671" s="42"/>
     </row>
     <row r="672" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B672" s="54"/>
-      <c r="C672" s="55"/>
+      <c r="B672" s="41"/>
+      <c r="C672" s="42"/>
     </row>
     <row r="673" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B673" s="54"/>
-      <c r="C673" s="55"/>
+      <c r="B673" s="41"/>
+      <c r="C673" s="42"/>
     </row>
     <row r="674" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B674" s="54"/>
-      <c r="C674" s="55"/>
+      <c r="B674" s="41"/>
+      <c r="C674" s="42"/>
     </row>
     <row r="675" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B675" s="54"/>
-      <c r="C675" s="55"/>
+      <c r="B675" s="41"/>
+      <c r="C675" s="42"/>
     </row>
     <row r="676" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B676" s="54"/>
-      <c r="C676" s="55"/>
+      <c r="B676" s="41"/>
+      <c r="C676" s="42"/>
     </row>
     <row r="677" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B677" s="54"/>
-      <c r="C677" s="55"/>
+      <c r="B677" s="41"/>
+      <c r="C677" s="42"/>
     </row>
     <row r="678" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B678" s="54"/>
-      <c r="C678" s="55"/>
+      <c r="B678" s="41"/>
+      <c r="C678" s="42"/>
     </row>
     <row r="679" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B679" s="54"/>
-      <c r="C679" s="55"/>
+      <c r="B679" s="41"/>
+      <c r="C679" s="42"/>
     </row>
     <row r="680" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B680" s="54"/>
-      <c r="C680" s="55"/>
+      <c r="B680" s="41"/>
+      <c r="C680" s="42"/>
     </row>
     <row r="681" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B681" s="54"/>
-      <c r="C681" s="55"/>
+      <c r="B681" s="41"/>
+      <c r="C681" s="42"/>
     </row>
     <row r="682" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B682" s="54"/>
-      <c r="C682" s="55"/>
+      <c r="B682" s="41"/>
+      <c r="C682" s="42"/>
     </row>
     <row r="683" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B683" s="54"/>
-      <c r="C683" s="55"/>
+      <c r="B683" s="41"/>
+      <c r="C683" s="42"/>
     </row>
     <row r="684" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B684" s="54"/>
-      <c r="C684" s="55"/>
+      <c r="B684" s="41"/>
+      <c r="C684" s="42"/>
     </row>
     <row r="685" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B685" s="54"/>
-      <c r="C685" s="55"/>
+      <c r="B685" s="41"/>
+      <c r="C685" s="42"/>
     </row>
     <row r="686" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B686" s="54"/>
-      <c r="C686" s="55"/>
+      <c r="B686" s="41"/>
+      <c r="C686" s="42"/>
     </row>
     <row r="687" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B687" s="54"/>
-      <c r="C687" s="55"/>
+      <c r="B687" s="41"/>
+      <c r="C687" s="42"/>
     </row>
     <row r="688" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B688" s="54"/>
-      <c r="C688" s="55"/>
+      <c r="B688" s="41"/>
+      <c r="C688" s="42"/>
     </row>
     <row r="689" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B689" s="54"/>
-      <c r="C689" s="55"/>
+      <c r="B689" s="41"/>
+      <c r="C689" s="42"/>
     </row>
     <row r="690" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B690" s="54"/>
-      <c r="C690" s="55"/>
+      <c r="B690" s="41"/>
+      <c r="C690" s="42"/>
     </row>
     <row r="691" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B691" s="54"/>
-      <c r="C691" s="55"/>
+      <c r="B691" s="41"/>
+      <c r="C691" s="42"/>
     </row>
     <row r="692" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B692" s="54"/>
-      <c r="C692" s="55"/>
+      <c r="B692" s="41"/>
+      <c r="C692" s="42"/>
     </row>
     <row r="693" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B693" s="54"/>
-      <c r="C693" s="55"/>
+      <c r="B693" s="41"/>
+      <c r="C693" s="42"/>
     </row>
     <row r="694" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B694" s="54"/>
-      <c r="C694" s="55"/>
+      <c r="B694" s="41"/>
+      <c r="C694" s="42"/>
     </row>
     <row r="695" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B695" s="54"/>
-      <c r="C695" s="55"/>
+      <c r="B695" s="41"/>
+      <c r="C695" s="42"/>
     </row>
     <row r="696" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B696" s="54"/>
-      <c r="C696" s="55"/>
+      <c r="B696" s="41"/>
+      <c r="C696" s="42"/>
     </row>
     <row r="697" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B697" s="54"/>
-      <c r="C697" s="55"/>
+      <c r="B697" s="41"/>
+      <c r="C697" s="42"/>
     </row>
     <row r="698" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B698" s="54"/>
-      <c r="C698" s="55"/>
+      <c r="B698" s="41"/>
+      <c r="C698" s="42"/>
     </row>
     <row r="699" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B699" s="54"/>
-      <c r="C699" s="55"/>
+      <c r="B699" s="41"/>
+      <c r="C699" s="42"/>
     </row>
     <row r="700" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B700" s="54"/>
-      <c r="C700" s="55"/>
+      <c r="B700" s="41"/>
+      <c r="C700" s="42"/>
     </row>
     <row r="701" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B701" s="54"/>
-      <c r="C701" s="55"/>
+      <c r="B701" s="41"/>
+      <c r="C701" s="42"/>
     </row>
     <row r="702" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B702" s="54"/>
-      <c r="C702" s="55"/>
+      <c r="B702" s="41"/>
+      <c r="C702" s="42"/>
     </row>
     <row r="703" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B703" s="54"/>
-      <c r="C703" s="55"/>
+      <c r="B703" s="41"/>
+      <c r="C703" s="42"/>
     </row>
     <row r="704" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B704" s="54"/>
-      <c r="C704" s="55"/>
+      <c r="B704" s="41"/>
+      <c r="C704" s="42"/>
     </row>
     <row r="705" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B705" s="54"/>
-      <c r="C705" s="55"/>
+      <c r="B705" s="41"/>
+      <c r="C705" s="42"/>
     </row>
     <row r="706" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B706" s="54"/>
-      <c r="C706" s="55"/>
+      <c r="B706" s="41"/>
+      <c r="C706" s="42"/>
     </row>
     <row r="707" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B707" s="54"/>
-      <c r="C707" s="55"/>
+      <c r="B707" s="41"/>
+      <c r="C707" s="42"/>
     </row>
     <row r="708" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B708" s="54"/>
-      <c r="C708" s="55"/>
+      <c r="B708" s="41"/>
+      <c r="C708" s="42"/>
     </row>
     <row r="709" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B709" s="54"/>
-      <c r="C709" s="55"/>
+      <c r="B709" s="41"/>
+      <c r="C709" s="42"/>
     </row>
     <row r="710" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B710" s="54"/>
-      <c r="C710" s="55"/>
+      <c r="B710" s="41"/>
+      <c r="C710" s="42"/>
     </row>
     <row r="711" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B711" s="54"/>
-      <c r="C711" s="55"/>
+      <c r="B711" s="41"/>
+      <c r="C711" s="42"/>
     </row>
     <row r="712" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B712" s="54"/>
-      <c r="C712" s="55"/>
+      <c r="B712" s="41"/>
+      <c r="C712" s="42"/>
     </row>
     <row r="713" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B713" s="54"/>
-      <c r="C713" s="55"/>
+      <c r="B713" s="41"/>
+      <c r="C713" s="42"/>
     </row>
     <row r="714" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B714" s="54"/>
-      <c r="C714" s="55"/>
+      <c r="B714" s="41"/>
+      <c r="C714" s="42"/>
     </row>
     <row r="715" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B715" s="54"/>
-      <c r="C715" s="55"/>
+      <c r="B715" s="41"/>
+      <c r="C715" s="42"/>
     </row>
     <row r="716" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B716" s="54"/>
-      <c r="C716" s="55"/>
+      <c r="B716" s="41"/>
+      <c r="C716" s="42"/>
     </row>
     <row r="717" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B717" s="54"/>
-      <c r="C717" s="55"/>
+      <c r="B717" s="41"/>
+      <c r="C717" s="42"/>
     </row>
     <row r="718" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B718" s="54"/>
-      <c r="C718" s="55"/>
+      <c r="B718" s="41"/>
+      <c r="C718" s="42"/>
     </row>
     <row r="719" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B719" s="54"/>
-      <c r="C719" s="55"/>
+      <c r="B719" s="41"/>
+      <c r="C719" s="42"/>
     </row>
     <row r="720" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B720" s="54"/>
-      <c r="C720" s="55"/>
+      <c r="B720" s="41"/>
+      <c r="C720" s="42"/>
     </row>
     <row r="721" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B721" s="54"/>
-      <c r="C721" s="55"/>
+      <c r="B721" s="41"/>
+      <c r="C721" s="42"/>
     </row>
     <row r="722" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B722" s="54"/>
-      <c r="C722" s="55"/>
+      <c r="B722" s="41"/>
+      <c r="C722" s="42"/>
     </row>
     <row r="723" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B723" s="54"/>
-      <c r="C723" s="55"/>
+      <c r="B723" s="41"/>
+      <c r="C723" s="42"/>
     </row>
     <row r="724" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B724" s="54"/>
-      <c r="C724" s="55"/>
+      <c r="B724" s="41"/>
+      <c r="C724" s="42"/>
     </row>
     <row r="725" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B725" s="54"/>
-      <c r="C725" s="55"/>
+      <c r="B725" s="41"/>
+      <c r="C725" s="42"/>
     </row>
     <row r="726" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B726" s="54"/>
-      <c r="C726" s="55"/>
+      <c r="B726" s="41"/>
+      <c r="C726" s="42"/>
     </row>
     <row r="727" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B727" s="54"/>
-      <c r="C727" s="55"/>
+      <c r="B727" s="41"/>
+      <c r="C727" s="42"/>
     </row>
     <row r="728" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B728" s="54"/>
-      <c r="C728" s="55"/>
+      <c r="B728" s="41"/>
+      <c r="C728" s="42"/>
     </row>
     <row r="729" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B729" s="54"/>
-      <c r="C729" s="55"/>
+      <c r="B729" s="41"/>
+      <c r="C729" s="42"/>
     </row>
     <row r="730" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B730" s="54"/>
-      <c r="C730" s="55"/>
+      <c r="B730" s="41"/>
+      <c r="C730" s="42"/>
     </row>
     <row r="731" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B731" s="54"/>
-      <c r="C731" s="55"/>
+      <c r="B731" s="41"/>
+      <c r="C731" s="42"/>
     </row>
     <row r="732" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B732" s="54"/>
-      <c r="C732" s="55"/>
+      <c r="B732" s="41"/>
+      <c r="C732" s="42"/>
     </row>
     <row r="733" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B733" s="54"/>
-      <c r="C733" s="55"/>
+      <c r="B733" s="41"/>
+      <c r="C733" s="42"/>
     </row>
     <row r="734" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B734" s="54"/>
-      <c r="C734" s="55"/>
+      <c r="B734" s="41"/>
+      <c r="C734" s="42"/>
     </row>
     <row r="735" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B735" s="54"/>
-      <c r="C735" s="55"/>
+      <c r="B735" s="41"/>
+      <c r="C735" s="42"/>
     </row>
     <row r="736" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B736" s="54"/>
-      <c r="C736" s="55"/>
+      <c r="B736" s="41"/>
+      <c r="C736" s="42"/>
     </row>
     <row r="737" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B737" s="54"/>
-      <c r="C737" s="55"/>
+      <c r="B737" s="41"/>
+      <c r="C737" s="42"/>
     </row>
     <row r="738" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B738" s="54"/>
-      <c r="C738" s="55"/>
+      <c r="B738" s="41"/>
+      <c r="C738" s="42"/>
     </row>
     <row r="739" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B739" s="54"/>
-      <c r="C739" s="55"/>
+      <c r="B739" s="41"/>
+      <c r="C739" s="42"/>
     </row>
     <row r="740" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B740" s="54"/>
-      <c r="C740" s="55"/>
+      <c r="B740" s="41"/>
+      <c r="C740" s="42"/>
     </row>
     <row r="741" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B741" s="54"/>
-      <c r="C741" s="55"/>
+      <c r="B741" s="41"/>
+      <c r="C741" s="42"/>
     </row>
     <row r="742" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B742" s="54"/>
-      <c r="C742" s="55"/>
+      <c r="B742" s="41"/>
+      <c r="C742" s="42"/>
     </row>
     <row r="743" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B743" s="54"/>
-      <c r="C743" s="55"/>
+      <c r="B743" s="41"/>
+      <c r="C743" s="42"/>
     </row>
     <row r="744" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B744" s="54"/>
-      <c r="C744" s="55"/>
+      <c r="B744" s="41"/>
+      <c r="C744" s="42"/>
     </row>
     <row r="745" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B745" s="54"/>
-      <c r="C745" s="55"/>
+      <c r="B745" s="41"/>
+      <c r="C745" s="42"/>
     </row>
     <row r="746" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B746" s="54"/>
-      <c r="C746" s="55"/>
+      <c r="B746" s="41"/>
+      <c r="C746" s="42"/>
     </row>
     <row r="747" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B747" s="54"/>
-      <c r="C747" s="55"/>
+      <c r="B747" s="41"/>
+      <c r="C747" s="42"/>
     </row>
     <row r="748" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B748" s="54"/>
-      <c r="C748" s="55"/>
+      <c r="B748" s="41"/>
+      <c r="C748" s="42"/>
     </row>
     <row r="749" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B749" s="54"/>
-      <c r="C749" s="55"/>
+      <c r="B749" s="41"/>
+      <c r="C749" s="42"/>
     </row>
     <row r="750" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B750" s="54"/>
-      <c r="C750" s="55"/>
+      <c r="B750" s="41"/>
+      <c r="C750" s="42"/>
     </row>
     <row r="751" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B751" s="54"/>
-      <c r="C751" s="55"/>
+      <c r="B751" s="41"/>
+      <c r="C751" s="42"/>
     </row>
     <row r="752" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B752" s="54"/>
-      <c r="C752" s="55"/>
+      <c r="B752" s="41"/>
+      <c r="C752" s="42"/>
     </row>
     <row r="753" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B753" s="54"/>
-      <c r="C753" s="55"/>
+      <c r="B753" s="41"/>
+      <c r="C753" s="42"/>
     </row>
     <row r="754" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B754" s="54"/>
-      <c r="C754" s="55"/>
+      <c r="B754" s="41"/>
+      <c r="C754" s="42"/>
     </row>
     <row r="755" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B755" s="54"/>
-      <c r="C755" s="55"/>
+      <c r="B755" s="41"/>
+      <c r="C755" s="42"/>
     </row>
     <row r="756" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B756" s="54"/>
-      <c r="C756" s="55"/>
+      <c r="B756" s="41"/>
+      <c r="C756" s="42"/>
     </row>
     <row r="757" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B757" s="54"/>
-      <c r="C757" s="55"/>
+      <c r="B757" s="41"/>
+      <c r="C757" s="42"/>
     </row>
     <row r="758" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B758" s="54"/>
-      <c r="C758" s="55"/>
+      <c r="B758" s="41"/>
+      <c r="C758" s="42"/>
     </row>
     <row r="759" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B759" s="54"/>
-      <c r="C759" s="55"/>
+      <c r="B759" s="41"/>
+      <c r="C759" s="42"/>
     </row>
     <row r="760" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B760" s="54"/>
-      <c r="C760" s="55"/>
+      <c r="B760" s="41"/>
+      <c r="C760" s="42"/>
     </row>
     <row r="761" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B761" s="54"/>
-      <c r="C761" s="55"/>
+      <c r="B761" s="41"/>
+      <c r="C761" s="42"/>
     </row>
     <row r="762" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B762" s="54"/>
-      <c r="C762" s="55"/>
+      <c r="B762" s="41"/>
+      <c r="C762" s="42"/>
     </row>
     <row r="763" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B763" s="54"/>
-      <c r="C763" s="55"/>
+      <c r="B763" s="41"/>
+      <c r="C763" s="42"/>
     </row>
     <row r="764" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B764" s="54"/>
-      <c r="C764" s="55"/>
+      <c r="B764" s="41"/>
+      <c r="C764" s="42"/>
     </row>
     <row r="765" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B765" s="54"/>
-      <c r="C765" s="55"/>
+      <c r="B765" s="41"/>
+      <c r="C765" s="42"/>
     </row>
     <row r="766" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B766" s="54"/>
-      <c r="C766" s="55"/>
+      <c r="B766" s="41"/>
+      <c r="C766" s="42"/>
     </row>
     <row r="767" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B767" s="54"/>
-      <c r="C767" s="55"/>
+      <c r="B767" s="41"/>
+      <c r="C767" s="42"/>
     </row>
     <row r="768" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B768" s="54"/>
-      <c r="C768" s="55"/>
+      <c r="B768" s="41"/>
+      <c r="C768" s="42"/>
     </row>
     <row r="769" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B769" s="54"/>
-      <c r="C769" s="55"/>
+      <c r="B769" s="41"/>
+      <c r="C769" s="42"/>
     </row>
     <row r="770" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B770" s="54"/>
-      <c r="C770" s="55"/>
+      <c r="B770" s="41"/>
+      <c r="C770" s="42"/>
     </row>
     <row r="771" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B771" s="54"/>
-      <c r="C771" s="55"/>
+      <c r="B771" s="41"/>
+      <c r="C771" s="42"/>
     </row>
     <row r="772" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B772" s="54"/>
-      <c r="C772" s="55"/>
+      <c r="B772" s="41"/>
+      <c r="C772" s="42"/>
     </row>
     <row r="773" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B773" s="54"/>
-      <c r="C773" s="55"/>
+      <c r="B773" s="41"/>
+      <c r="C773" s="42"/>
     </row>
     <row r="774" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B774" s="54"/>
-      <c r="C774" s="55"/>
+      <c r="B774" s="41"/>
+      <c r="C774" s="42"/>
     </row>
     <row r="775" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B775" s="54"/>
-      <c r="C775" s="55"/>
+      <c r="B775" s="41"/>
+      <c r="C775" s="42"/>
     </row>
     <row r="776" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B776" s="54"/>
-      <c r="C776" s="55"/>
+      <c r="B776" s="41"/>
+      <c r="C776" s="42"/>
     </row>
     <row r="777" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B777" s="54"/>
-      <c r="C777" s="55"/>
+      <c r="B777" s="41"/>
+      <c r="C777" s="42"/>
     </row>
     <row r="778" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B778" s="54"/>
-      <c r="C778" s="55"/>
+      <c r="B778" s="41"/>
+      <c r="C778" s="42"/>
     </row>
     <row r="779" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B779" s="54"/>
-      <c r="C779" s="55"/>
+      <c r="B779" s="41"/>
+      <c r="C779" s="42"/>
     </row>
     <row r="780" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B780" s="54"/>
-      <c r="C780" s="55"/>
+      <c r="B780" s="41"/>
+      <c r="C780" s="42"/>
     </row>
     <row r="781" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B781" s="54"/>
-      <c r="C781" s="55"/>
+      <c r="B781" s="41"/>
+      <c r="C781" s="42"/>
     </row>
     <row r="782" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B782" s="54"/>
-      <c r="C782" s="55"/>
+      <c r="B782" s="41"/>
+      <c r="C782" s="42"/>
     </row>
     <row r="783" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B783" s="54"/>
-      <c r="C783" s="55"/>
+      <c r="B783" s="41"/>
+      <c r="C783" s="42"/>
     </row>
     <row r="784" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B784" s="54"/>
-      <c r="C784" s="55"/>
+      <c r="B784" s="41"/>
+      <c r="C784" s="42"/>
     </row>
     <row r="785" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B785" s="54"/>
-      <c r="C785" s="55"/>
+      <c r="B785" s="41"/>
+      <c r="C785" s="42"/>
     </row>
     <row r="786" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B786" s="54"/>
-      <c r="C786" s="55"/>
+      <c r="B786" s="41"/>
+      <c r="C786" s="42"/>
     </row>
     <row r="787" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B787" s="54"/>
-      <c r="C787" s="55"/>
+      <c r="B787" s="41"/>
+      <c r="C787" s="42"/>
     </row>
     <row r="788" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B788" s="54"/>
-      <c r="C788" s="55"/>
+      <c r="B788" s="41"/>
+      <c r="C788" s="42"/>
     </row>
     <row r="789" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B789" s="54"/>
-      <c r="C789" s="55"/>
+      <c r="B789" s="41"/>
+      <c r="C789" s="42"/>
     </row>
     <row r="790" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B790" s="54"/>
-      <c r="C790" s="55"/>
+      <c r="B790" s="41"/>
+      <c r="C790" s="42"/>
     </row>
     <row r="791" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B791" s="54"/>
-      <c r="C791" s="55"/>
+      <c r="B791" s="41"/>
+      <c r="C791" s="42"/>
     </row>
     <row r="792" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B792" s="54"/>
-      <c r="C792" s="55"/>
+      <c r="B792" s="41"/>
+      <c r="C792" s="42"/>
     </row>
     <row r="793" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B793" s="54"/>
-      <c r="C793" s="55"/>
+      <c r="B793" s="41"/>
+      <c r="C793" s="42"/>
     </row>
     <row r="794" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B794" s="54"/>
-      <c r="C794" s="55"/>
+      <c r="B794" s="41"/>
+      <c r="C794" s="42"/>
     </row>
     <row r="795" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B795" s="54"/>
-      <c r="C795" s="55"/>
+      <c r="B795" s="41"/>
+      <c r="C795" s="42"/>
     </row>
     <row r="796" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B796" s="54"/>
-      <c r="C796" s="55"/>
+      <c r="B796" s="41"/>
+      <c r="C796" s="42"/>
     </row>
     <row r="797" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B797" s="54"/>
-      <c r="C797" s="55"/>
+      <c r="B797" s="41"/>
+      <c r="C797" s="42"/>
     </row>
     <row r="798" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B798" s="54"/>
-      <c r="C798" s="55"/>
+      <c r="B798" s="41"/>
+      <c r="C798" s="42"/>
     </row>
     <row r="799" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B799" s="54"/>
-      <c r="C799" s="55"/>
+      <c r="B799" s="41"/>
+      <c r="C799" s="42"/>
     </row>
     <row r="800" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B800" s="54"/>
-      <c r="C800" s="55"/>
+      <c r="B800" s="41"/>
+      <c r="C800" s="42"/>
     </row>
     <row r="801" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B801" s="54"/>
-      <c r="C801" s="55"/>
+      <c r="B801" s="41"/>
+      <c r="C801" s="42"/>
     </row>
     <row r="802" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B802" s="54"/>
-      <c r="C802" s="55"/>
+      <c r="B802" s="41"/>
+      <c r="C802" s="42"/>
     </row>
     <row r="803" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B803" s="54"/>
-      <c r="C803" s="55"/>
+      <c r="B803" s="41"/>
+      <c r="C803" s="42"/>
     </row>
     <row r="804" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B804" s="54"/>
-      <c r="C804" s="55"/>
+      <c r="B804" s="41"/>
+      <c r="C804" s="42"/>
     </row>
     <row r="805" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B805" s="54"/>
-      <c r="C805" s="55"/>
+      <c r="B805" s="41"/>
+      <c r="C805" s="42"/>
     </row>
     <row r="806" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B806" s="54"/>
-      <c r="C806" s="55"/>
+      <c r="B806" s="41"/>
+      <c r="C806" s="42"/>
     </row>
     <row r="807" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B807" s="54"/>
-      <c r="C807" s="55"/>
+      <c r="B807" s="41"/>
+      <c r="C807" s="42"/>
     </row>
     <row r="808" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B808" s="54"/>
-      <c r="C808" s="55"/>
+      <c r="B808" s="41"/>
+      <c r="C808" s="42"/>
     </row>
     <row r="809" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B809" s="54"/>
-      <c r="C809" s="55"/>
+      <c r="B809" s="41"/>
+      <c r="C809" s="42"/>
     </row>
     <row r="810" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B810" s="54"/>
-      <c r="C810" s="55"/>
+      <c r="B810" s="41"/>
+      <c r="C810" s="42"/>
     </row>
     <row r="811" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B811" s="54"/>
-      <c r="C811" s="55"/>
+      <c r="B811" s="41"/>
+      <c r="C811" s="42"/>
     </row>
     <row r="812" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B812" s="54"/>
-      <c r="C812" s="55"/>
+      <c r="B812" s="41"/>
+      <c r="C812" s="42"/>
     </row>
     <row r="813" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B813" s="54"/>
-      <c r="C813" s="55"/>
+      <c r="B813" s="41"/>
+      <c r="C813" s="42"/>
     </row>
     <row r="814" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B814" s="54"/>
-      <c r="C814" s="55"/>
+      <c r="B814" s="41"/>
+      <c r="C814" s="42"/>
     </row>
     <row r="815" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B815" s="54"/>
-      <c r="C815" s="55"/>
+      <c r="B815" s="41"/>
+      <c r="C815" s="42"/>
     </row>
     <row r="816" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B816" s="54"/>
-      <c r="C816" s="55"/>
+      <c r="B816" s="41"/>
+      <c r="C816" s="42"/>
     </row>
     <row r="817" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B817" s="54"/>
-      <c r="C817" s="55"/>
+      <c r="B817" s="41"/>
+      <c r="C817" s="42"/>
     </row>
     <row r="818" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B818" s="54"/>
-      <c r="C818" s="55"/>
+      <c r="B818" s="41"/>
+      <c r="C818" s="42"/>
     </row>
     <row r="819" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B819" s="54"/>
-      <c r="C819" s="55"/>
+      <c r="B819" s="41"/>
+      <c r="C819" s="42"/>
     </row>
     <row r="820" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B820" s="54"/>
-      <c r="C820" s="55"/>
+      <c r="B820" s="41"/>
+      <c r="C820" s="42"/>
     </row>
     <row r="821" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B821" s="54"/>
-      <c r="C821" s="55"/>
+      <c r="B821" s="41"/>
+      <c r="C821" s="42"/>
     </row>
     <row r="822" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B822" s="54"/>
-      <c r="C822" s="55"/>
+      <c r="B822" s="41"/>
+      <c r="C822" s="42"/>
     </row>
     <row r="823" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B823" s="54"/>
-      <c r="C823" s="55"/>
+      <c r="B823" s="41"/>
+      <c r="C823" s="42"/>
     </row>
     <row r="824" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B824" s="54"/>
-      <c r="C824" s="55"/>
+      <c r="B824" s="41"/>
+      <c r="C824" s="42"/>
     </row>
     <row r="825" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B825" s="54"/>
-      <c r="C825" s="55"/>
+      <c r="B825" s="41"/>
+      <c r="C825" s="42"/>
     </row>
     <row r="826" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B826" s="54"/>
-      <c r="C826" s="55"/>
+      <c r="B826" s="41"/>
+      <c r="C826" s="42"/>
     </row>
     <row r="827" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B827" s="54"/>
-      <c r="C827" s="55"/>
+      <c r="B827" s="41"/>
+      <c r="C827" s="42"/>
     </row>
     <row r="828" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B828" s="54"/>
-      <c r="C828" s="55"/>
+      <c r="B828" s="41"/>
+      <c r="C828" s="42"/>
     </row>
     <row r="829" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B829" s="54"/>
-      <c r="C829" s="55"/>
+      <c r="B829" s="41"/>
+      <c r="C829" s="42"/>
     </row>
     <row r="830" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B830" s="54"/>
-      <c r="C830" s="55"/>
+      <c r="B830" s="41"/>
+      <c r="C830" s="42"/>
     </row>
     <row r="831" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B831" s="54"/>
-      <c r="C831" s="55"/>
+      <c r="B831" s="41"/>
+      <c r="C831" s="42"/>
     </row>
     <row r="832" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B832" s="54"/>
-      <c r="C832" s="55"/>
+      <c r="B832" s="41"/>
+      <c r="C832" s="42"/>
     </row>
     <row r="833" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B833" s="54"/>
-      <c r="C833" s="55"/>
+      <c r="B833" s="41"/>
+      <c r="C833" s="42"/>
     </row>
     <row r="834" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B834" s="54"/>
-      <c r="C834" s="55"/>
+      <c r="B834" s="41"/>
+      <c r="C834" s="42"/>
     </row>
     <row r="835" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B835" s="54"/>
-      <c r="C835" s="55"/>
+      <c r="B835" s="41"/>
+      <c r="C835" s="42"/>
     </row>
     <row r="836" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B836" s="54"/>
-      <c r="C836" s="55"/>
+      <c r="B836" s="41"/>
+      <c r="C836" s="42"/>
     </row>
     <row r="837" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B837" s="54"/>
-      <c r="C837" s="55"/>
+      <c r="B837" s="41"/>
+      <c r="C837" s="42"/>
     </row>
     <row r="838" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B838" s="54"/>
-      <c r="C838" s="55"/>
+      <c r="B838" s="41"/>
+      <c r="C838" s="42"/>
     </row>
     <row r="839" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B839" s="54"/>
-      <c r="C839" s="55"/>
+      <c r="B839" s="41"/>
+      <c r="C839" s="42"/>
     </row>
     <row r="840" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B840" s="54"/>
-      <c r="C840" s="55"/>
+      <c r="B840" s="41"/>
+      <c r="C840" s="42"/>
     </row>
     <row r="841" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B841" s="54"/>
-      <c r="C841" s="55"/>
+      <c r="B841" s="41"/>
+      <c r="C841" s="42"/>
     </row>
     <row r="842" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B842" s="54"/>
-      <c r="C842" s="55"/>
+      <c r="B842" s="41"/>
+      <c r="C842" s="42"/>
     </row>
     <row r="843" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B843" s="54"/>
-      <c r="C843" s="55"/>
+      <c r="B843" s="41"/>
+      <c r="C843" s="42"/>
     </row>
     <row r="844" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B844" s="54"/>
-      <c r="C844" s="55"/>
+      <c r="B844" s="41"/>
+      <c r="C844" s="42"/>
     </row>
     <row r="845" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B845" s="54"/>
-      <c r="C845" s="55"/>
+      <c r="B845" s="41"/>
+      <c r="C845" s="42"/>
     </row>
     <row r="846" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B846" s="54"/>
-      <c r="C846" s="55"/>
+      <c r="B846" s="41"/>
+      <c r="C846" s="42"/>
     </row>
     <row r="847" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B847" s="54"/>
-      <c r="C847" s="55"/>
+      <c r="B847" s="41"/>
+      <c r="C847" s="42"/>
     </row>
     <row r="848" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B848" s="54"/>
-      <c r="C848" s="55"/>
+      <c r="B848" s="41"/>
+      <c r="C848" s="42"/>
     </row>
     <row r="849" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B849" s="54"/>
-      <c r="C849" s="55"/>
+      <c r="B849" s="41"/>
+      <c r="C849" s="42"/>
     </row>
     <row r="850" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B850" s="54"/>
-      <c r="C850" s="55"/>
+      <c r="B850" s="41"/>
+      <c r="C850" s="42"/>
     </row>
     <row r="851" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B851" s="54"/>
-      <c r="C851" s="55"/>
+      <c r="B851" s="41"/>
+      <c r="C851" s="42"/>
     </row>
     <row r="852" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B852" s="54"/>
-      <c r="C852" s="55"/>
+      <c r="B852" s="41"/>
+      <c r="C852" s="42"/>
     </row>
     <row r="853" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B853" s="54"/>
-      <c r="C853" s="55"/>
+      <c r="B853" s="41"/>
+      <c r="C853" s="42"/>
     </row>
     <row r="854" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B854" s="54"/>
-      <c r="C854" s="55"/>
+      <c r="B854" s="41"/>
+      <c r="C854" s="42"/>
     </row>
     <row r="855" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B855" s="54"/>
-      <c r="C855" s="55"/>
+      <c r="B855" s="41"/>
+      <c r="C855" s="42"/>
     </row>
     <row r="856" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B856" s="54"/>
-      <c r="C856" s="55"/>
+      <c r="B856" s="41"/>
+      <c r="C856" s="42"/>
     </row>
     <row r="857" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B857" s="54"/>
-      <c r="C857" s="55"/>
+      <c r="B857" s="41"/>
+      <c r="C857" s="42"/>
     </row>
     <row r="858" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B858" s="54"/>
-      <c r="C858" s="55"/>
+      <c r="B858" s="41"/>
+      <c r="C858" s="42"/>
     </row>
     <row r="859" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B859" s="54"/>
-      <c r="C859" s="55"/>
+      <c r="B859" s="41"/>
+      <c r="C859" s="42"/>
     </row>
     <row r="860" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B860" s="54"/>
-      <c r="C860" s="55"/>
+      <c r="B860" s="41"/>
+      <c r="C860" s="42"/>
     </row>
     <row r="861" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B861" s="54"/>
-      <c r="C861" s="55"/>
+      <c r="B861" s="41"/>
+      <c r="C861" s="42"/>
     </row>
     <row r="862" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B862" s="54"/>
-      <c r="C862" s="55"/>
+      <c r="B862" s="41"/>
+      <c r="C862" s="42"/>
     </row>
     <row r="863" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B863" s="54"/>
-      <c r="C863" s="55"/>
+      <c r="B863" s="41"/>
+      <c r="C863" s="42"/>
     </row>
     <row r="864" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B864" s="54"/>
-      <c r="C864" s="55"/>
+      <c r="B864" s="41"/>
+      <c r="C864" s="42"/>
     </row>
     <row r="865" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B865" s="54"/>
-      <c r="C865" s="55"/>
+      <c r="B865" s="41"/>
+      <c r="C865" s="42"/>
     </row>
     <row r="866" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B866" s="54"/>
-      <c r="C866" s="55"/>
+      <c r="B866" s="41"/>
+      <c r="C866" s="42"/>
     </row>
     <row r="867" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B867" s="54"/>
-      <c r="C867" s="55"/>
+      <c r="B867" s="41"/>
+      <c r="C867" s="42"/>
     </row>
     <row r="868" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B868" s="54"/>
-      <c r="C868" s="55"/>
+      <c r="B868" s="41"/>
+      <c r="C868" s="42"/>
     </row>
     <row r="869" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B869" s="54"/>
-      <c r="C869" s="55"/>
+      <c r="B869" s="41"/>
+      <c r="C869" s="42"/>
     </row>
     <row r="870" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B870" s="54"/>
-      <c r="C870" s="55"/>
+      <c r="B870" s="41"/>
+      <c r="C870" s="42"/>
     </row>
     <row r="871" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B871" s="54"/>
-      <c r="C871" s="55"/>
+      <c r="B871" s="41"/>
+      <c r="C871" s="42"/>
     </row>
     <row r="872" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B872" s="54"/>
-      <c r="C872" s="55"/>
+      <c r="B872" s="41"/>
+      <c r="C872" s="42"/>
     </row>
     <row r="873" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B873" s="54"/>
-      <c r="C873" s="55"/>
+      <c r="B873" s="41"/>
+      <c r="C873" s="42"/>
     </row>
     <row r="874" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B874" s="54"/>
-      <c r="C874" s="55"/>
+      <c r="B874" s="41"/>
+      <c r="C874" s="42"/>
     </row>
     <row r="875" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B875" s="54"/>
-      <c r="C875" s="55"/>
+      <c r="B875" s="41"/>
+      <c r="C875" s="42"/>
     </row>
     <row r="876" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B876" s="54"/>
-      <c r="C876" s="55"/>
+      <c r="B876" s="41"/>
+      <c r="C876" s="42"/>
     </row>
     <row r="877" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B877" s="54"/>
-      <c r="C877" s="55"/>
+      <c r="B877" s="41"/>
+      <c r="C877" s="42"/>
     </row>
     <row r="878" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B878" s="54"/>
-      <c r="C878" s="55"/>
+      <c r="B878" s="41"/>
+      <c r="C878" s="42"/>
     </row>
     <row r="879" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B879" s="54"/>
-      <c r="C879" s="55"/>
+      <c r="B879" s="41"/>
+      <c r="C879" s="42"/>
     </row>
     <row r="880" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B880" s="54"/>
-      <c r="C880" s="55"/>
+      <c r="B880" s="41"/>
+      <c r="C880" s="42"/>
     </row>
     <row r="881" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B881" s="54"/>
-      <c r="C881" s="55"/>
+      <c r="B881" s="41"/>
+      <c r="C881" s="42"/>
     </row>
     <row r="882" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B882" s="54"/>
-      <c r="C882" s="55"/>
+      <c r="B882" s="41"/>
+      <c r="C882" s="42"/>
     </row>
     <row r="883" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B883" s="54"/>
-      <c r="C883" s="55"/>
+      <c r="B883" s="41"/>
+      <c r="C883" s="42"/>
     </row>
     <row r="884" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B884" s="54"/>
-      <c r="C884" s="55"/>
+      <c r="B884" s="41"/>
+      <c r="C884" s="42"/>
     </row>
     <row r="885" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B885" s="54"/>
-      <c r="C885" s="55"/>
+      <c r="B885" s="41"/>
+      <c r="C885" s="42"/>
     </row>
     <row r="886" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B886" s="54"/>
-      <c r="C886" s="55"/>
+      <c r="B886" s="41"/>
+      <c r="C886" s="42"/>
     </row>
     <row r="887" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B887" s="54"/>
-      <c r="C887" s="55"/>
+      <c r="B887" s="41"/>
+      <c r="C887" s="42"/>
     </row>
     <row r="888" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B888" s="54"/>
-      <c r="C888" s="55"/>
+      <c r="B888" s="41"/>
+      <c r="C888" s="42"/>
     </row>
     <row r="889" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B889" s="54"/>
-      <c r="C889" s="55"/>
+      <c r="B889" s="41"/>
+      <c r="C889" s="42"/>
     </row>
     <row r="890" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B890" s="54"/>
-      <c r="C890" s="55"/>
+      <c r="B890" s="41"/>
+      <c r="C890" s="42"/>
     </row>
     <row r="891" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B891" s="54"/>
-      <c r="C891" s="55"/>
+      <c r="B891" s="41"/>
+      <c r="C891" s="42"/>
     </row>
     <row r="892" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B892" s="54"/>
-      <c r="C892" s="55"/>
+      <c r="B892" s="41"/>
+      <c r="C892" s="42"/>
     </row>
     <row r="893" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B893" s="54"/>
-      <c r="C893" s="55"/>
+      <c r="B893" s="41"/>
+      <c r="C893" s="42"/>
     </row>
     <row r="894" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B894" s="54"/>
-      <c r="C894" s="55"/>
+      <c r="B894" s="41"/>
+      <c r="C894" s="42"/>
     </row>
     <row r="895" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B895" s="54"/>
-      <c r="C895" s="55"/>
+      <c r="B895" s="41"/>
+      <c r="C895" s="42"/>
     </row>
     <row r="896" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B896" s="54"/>
-      <c r="C896" s="55"/>
+      <c r="B896" s="41"/>
+      <c r="C896" s="42"/>
     </row>
     <row r="897" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B897" s="54"/>
-      <c r="C897" s="55"/>
+      <c r="B897" s="41"/>
+      <c r="C897" s="42"/>
     </row>
     <row r="898" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B898" s="54"/>
-      <c r="C898" s="55"/>
+      <c r="B898" s="41"/>
+      <c r="C898" s="42"/>
     </row>
     <row r="899" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B899" s="54"/>
-      <c r="C899" s="55"/>
+      <c r="B899" s="41"/>
+      <c r="C899" s="42"/>
     </row>
     <row r="900" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B900" s="54"/>
-      <c r="C900" s="55"/>
+      <c r="B900" s="41"/>
+      <c r="C900" s="42"/>
     </row>
     <row r="901" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B901" s="54"/>
-      <c r="C901" s="55"/>
+      <c r="B901" s="41"/>
+      <c r="C901" s="42"/>
     </row>
     <row r="902" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B902" s="54"/>
-      <c r="C902" s="55"/>
+      <c r="B902" s="41"/>
+      <c r="C902" s="42"/>
     </row>
     <row r="903" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B903" s="54"/>
-      <c r="C903" s="55"/>
+      <c r="B903" s="41"/>
+      <c r="C903" s="42"/>
     </row>
     <row r="904" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B904" s="54"/>
-      <c r="C904" s="55"/>
+      <c r="B904" s="41"/>
+      <c r="C904" s="42"/>
     </row>
     <row r="905" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B905" s="54"/>
-      <c r="C905" s="55"/>
+      <c r="B905" s="41"/>
+      <c r="C905" s="42"/>
     </row>
     <row r="906" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B906" s="54"/>
-      <c r="C906" s="55"/>
+      <c r="B906" s="41"/>
+      <c r="C906" s="42"/>
     </row>
     <row r="907" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B907" s="54"/>
-      <c r="C907" s="55"/>
+      <c r="B907" s="41"/>
+      <c r="C907" s="42"/>
     </row>
     <row r="908" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B908" s="54"/>
-      <c r="C908" s="55"/>
+      <c r="B908" s="41"/>
+      <c r="C908" s="42"/>
     </row>
     <row r="909" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B909" s="54"/>
-      <c r="C909" s="55"/>
+      <c r="B909" s="41"/>
+      <c r="C909" s="42"/>
     </row>
     <row r="910" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B910" s="54"/>
-      <c r="C910" s="55"/>
+      <c r="B910" s="41"/>
+      <c r="C910" s="42"/>
     </row>
     <row r="911" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B911" s="54"/>
-      <c r="C911" s="55"/>
+      <c r="B911" s="41"/>
+      <c r="C911" s="42"/>
     </row>
     <row r="912" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B912" s="54"/>
-      <c r="C912" s="55"/>
+      <c r="B912" s="41"/>
+      <c r="C912" s="42"/>
     </row>
     <row r="913" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B913" s="54"/>
-      <c r="C913" s="55"/>
+      <c r="B913" s="41"/>
+      <c r="C913" s="42"/>
     </row>
     <row r="914" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B914" s="54"/>
-      <c r="C914" s="55"/>
+      <c r="B914" s="41"/>
+      <c r="C914" s="42"/>
     </row>
     <row r="915" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B915" s="54"/>
-      <c r="C915" s="55"/>
+      <c r="B915" s="41"/>
+      <c r="C915" s="42"/>
     </row>
     <row r="916" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B916" s="54"/>
-      <c r="C916" s="55"/>
+      <c r="B916" s="41"/>
+      <c r="C916" s="42"/>
     </row>
     <row r="917" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B917" s="54"/>
-      <c r="C917" s="55"/>
+      <c r="B917" s="41"/>
+      <c r="C917" s="42"/>
     </row>
     <row r="918" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B918" s="54"/>
-      <c r="C918" s="55"/>
+      <c r="B918" s="41"/>
+      <c r="C918" s="42"/>
     </row>
     <row r="919" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B919" s="54"/>
-      <c r="C919" s="55"/>
+      <c r="B919" s="41"/>
+      <c r="C919" s="42"/>
     </row>
     <row r="920" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B920" s="54"/>
-      <c r="C920" s="55"/>
+      <c r="B920" s="41"/>
+      <c r="C920" s="42"/>
     </row>
     <row r="921" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B921" s="54"/>
-      <c r="C921" s="55"/>
+      <c r="B921" s="41"/>
+      <c r="C921" s="42"/>
     </row>
     <row r="922" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B922" s="54"/>
-      <c r="C922" s="55"/>
+      <c r="B922" s="41"/>
+      <c r="C922" s="42"/>
     </row>
     <row r="923" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B923" s="54"/>
-      <c r="C923" s="55"/>
+      <c r="B923" s="41"/>
+      <c r="C923" s="42"/>
     </row>
     <row r="924" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B924" s="54"/>
-      <c r="C924" s="55"/>
+      <c r="B924" s="41"/>
+      <c r="C924" s="42"/>
     </row>
     <row r="925" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B925" s="54"/>
-      <c r="C925" s="55"/>
+      <c r="B925" s="41"/>
+      <c r="C925" s="42"/>
     </row>
     <row r="926" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B926" s="54"/>
-      <c r="C926" s="55"/>
+      <c r="B926" s="41"/>
+      <c r="C926" s="42"/>
     </row>
     <row r="927" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B927" s="54"/>
-      <c r="C927" s="55"/>
+      <c r="B927" s="41"/>
+      <c r="C927" s="42"/>
     </row>
     <row r="928" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B928" s="54"/>
-      <c r="C928" s="55"/>
+      <c r="B928" s="41"/>
+      <c r="C928" s="42"/>
     </row>
     <row r="929" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B929" s="54"/>
-      <c r="C929" s="55"/>
+      <c r="B929" s="41"/>
+      <c r="C929" s="42"/>
     </row>
     <row r="930" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B930" s="54"/>
-      <c r="C930" s="55"/>
+      <c r="B930" s="41"/>
+      <c r="C930" s="42"/>
     </row>
     <row r="931" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B931" s="54"/>
-      <c r="C931" s="55"/>
+      <c r="B931" s="41"/>
+      <c r="C931" s="42"/>
     </row>
     <row r="932" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B932" s="54"/>
-      <c r="C932" s="55"/>
+      <c r="B932" s="41"/>
+      <c r="C932" s="42"/>
     </row>
     <row r="933" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B933" s="54"/>
-      <c r="C933" s="55"/>
+      <c r="B933" s="41"/>
+      <c r="C933" s="42"/>
     </row>
     <row r="934" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B934" s="54"/>
-      <c r="C934" s="55"/>
+      <c r="B934" s="41"/>
+      <c r="C934" s="42"/>
     </row>
     <row r="935" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B935" s="54"/>
-      <c r="C935" s="55"/>
+      <c r="B935" s="41"/>
+      <c r="C935" s="42"/>
     </row>
     <row r="936" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B936" s="54"/>
-      <c r="C936" s="55"/>
+      <c r="B936" s="41"/>
+      <c r="C936" s="42"/>
     </row>
     <row r="937" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B937" s="54"/>
-      <c r="C937" s="55"/>
+      <c r="B937" s="41"/>
+      <c r="C937" s="42"/>
     </row>
     <row r="938" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B938" s="54"/>
-      <c r="C938" s="55"/>
+      <c r="B938" s="41"/>
+      <c r="C938" s="42"/>
     </row>
     <row r="939" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B939" s="54"/>
-      <c r="C939" s="55"/>
+      <c r="B939" s="41"/>
+      <c r="C939" s="42"/>
     </row>
     <row r="940" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B940" s="54"/>
-      <c r="C940" s="55"/>
+      <c r="B940" s="41"/>
+      <c r="C940" s="42"/>
     </row>
     <row r="941" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B941" s="54"/>
-      <c r="C941" s="55"/>
+      <c r="B941" s="41"/>
+      <c r="C941" s="42"/>
     </row>
     <row r="942" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B942" s="54"/>
-      <c r="C942" s="55"/>
+      <c r="B942" s="41"/>
+      <c r="C942" s="42"/>
     </row>
     <row r="943" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B943" s="54"/>
-      <c r="C943" s="55"/>
+      <c r="B943" s="41"/>
+      <c r="C943" s="42"/>
     </row>
     <row r="944" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B944" s="54"/>
-      <c r="C944" s="55"/>
+      <c r="B944" s="41"/>
+      <c r="C944" s="42"/>
     </row>
     <row r="945" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B945" s="54"/>
-      <c r="C945" s="55"/>
+      <c r="B945" s="41"/>
+      <c r="C945" s="42"/>
     </row>
     <row r="946" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B946" s="54"/>
-      <c r="C946" s="55"/>
+      <c r="B946" s="41"/>
+      <c r="C946" s="42"/>
     </row>
     <row r="947" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B947" s="54"/>
-      <c r="C947" s="55"/>
+      <c r="B947" s="41"/>
+      <c r="C947" s="42"/>
     </row>
     <row r="948" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B948" s="54"/>
-      <c r="C948" s="55"/>
+      <c r="B948" s="41"/>
+      <c r="C948" s="42"/>
     </row>
     <row r="949" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B949" s="54"/>
-      <c r="C949" s="55"/>
+      <c r="B949" s="41"/>
+      <c r="C949" s="42"/>
     </row>
     <row r="950" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B950" s="54"/>
-      <c r="C950" s="55"/>
+      <c r="B950" s="41"/>
+      <c r="C950" s="42"/>
     </row>
     <row r="951" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B951" s="54"/>
-      <c r="C951" s="55"/>
+      <c r="B951" s="41"/>
+      <c r="C951" s="42"/>
     </row>
     <row r="952" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B952" s="54"/>
-      <c r="C952" s="55"/>
+      <c r="B952" s="41"/>
+      <c r="C952" s="42"/>
     </row>
     <row r="953" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B953" s="54"/>
-      <c r="C953" s="55"/>
+      <c r="B953" s="41"/>
+      <c r="C953" s="42"/>
     </row>
     <row r="954" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B954" s="54"/>
-      <c r="C954" s="55"/>
+      <c r="B954" s="41"/>
+      <c r="C954" s="42"/>
     </row>
     <row r="955" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B955" s="54"/>
-      <c r="C955" s="55"/>
+      <c r="B955" s="41"/>
+      <c r="C955" s="42"/>
     </row>
     <row r="956" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B956" s="54"/>
-      <c r="C956" s="55"/>
+      <c r="B956" s="41"/>
+      <c r="C956" s="42"/>
     </row>
     <row r="957" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B957" s="54"/>
-      <c r="C957" s="55"/>
+      <c r="B957" s="41"/>
+      <c r="C957" s="42"/>
     </row>
     <row r="958" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B958" s="54"/>
-      <c r="C958" s="55"/>
+      <c r="B958" s="41"/>
+      <c r="C958" s="42"/>
     </row>
     <row r="959" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B959" s="54"/>
-      <c r="C959" s="55"/>
+      <c r="B959" s="41"/>
+      <c r="C959" s="42"/>
     </row>
     <row r="960" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B960" s="54"/>
-      <c r="C960" s="55"/>
+      <c r="B960" s="41"/>
+      <c r="C960" s="42"/>
     </row>
     <row r="961" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B961" s="54"/>
-      <c r="C961" s="55"/>
+      <c r="B961" s="41"/>
+      <c r="C961" s="42"/>
     </row>
     <row r="962" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B962" s="54"/>
-      <c r="C962" s="55"/>
+      <c r="B962" s="41"/>
+      <c r="C962" s="42"/>
     </row>
     <row r="963" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B963" s="54"/>
-      <c r="C963" s="55"/>
+      <c r="B963" s="41"/>
+      <c r="C963" s="42"/>
     </row>
     <row r="964" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B964" s="54"/>
-      <c r="C964" s="55"/>
+      <c r="B964" s="41"/>
+      <c r="C964" s="42"/>
     </row>
     <row r="965" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B965" s="54"/>
-      <c r="C965" s="55"/>
+      <c r="B965" s="41"/>
+      <c r="C965" s="42"/>
     </row>
     <row r="966" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B966" s="54"/>
-      <c r="C966" s="55"/>
+      <c r="B966" s="41"/>
+      <c r="C966" s="42"/>
     </row>
     <row r="967" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B967" s="54"/>
-      <c r="C967" s="55"/>
+      <c r="B967" s="41"/>
+      <c r="C967" s="42"/>
     </row>
     <row r="968" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B968" s="54"/>
-      <c r="C968" s="55"/>
+      <c r="B968" s="41"/>
+      <c r="C968" s="42"/>
     </row>
     <row r="969" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B969" s="54"/>
-      <c r="C969" s="55"/>
+      <c r="B969" s="41"/>
+      <c r="C969" s="42"/>
     </row>
     <row r="970" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B970" s="54"/>
-      <c r="C970" s="55"/>
+      <c r="B970" s="41"/>
+      <c r="C970" s="42"/>
     </row>
     <row r="971" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B971" s="54"/>
-      <c r="C971" s="55"/>
+      <c r="B971" s="41"/>
+      <c r="C971" s="42"/>
     </row>
     <row r="972" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B972" s="54"/>
-      <c r="C972" s="55"/>
+      <c r="B972" s="41"/>
+      <c r="C972" s="42"/>
     </row>
     <row r="973" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B973" s="54"/>
-      <c r="C973" s="55"/>
+      <c r="B973" s="41"/>
+      <c r="C973" s="42"/>
     </row>
     <row r="974" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B974" s="54"/>
-      <c r="C974" s="55"/>
+      <c r="B974" s="41"/>
+      <c r="C974" s="42"/>
     </row>
     <row r="975" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B975" s="54"/>
-      <c r="C975" s="55"/>
+      <c r="B975" s="41"/>
+      <c r="C975" s="42"/>
     </row>
     <row r="976" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B976" s="54"/>
-      <c r="C976" s="55"/>
+      <c r="B976" s="41"/>
+      <c r="C976" s="42"/>
     </row>
     <row r="977" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B977" s="54"/>
-      <c r="C977" s="55"/>
+      <c r="B977" s="41"/>
+      <c r="C977" s="42"/>
     </row>
     <row r="978" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B978" s="54"/>
-      <c r="C978" s="55"/>
+      <c r="B978" s="41"/>
+      <c r="C978" s="42"/>
     </row>
     <row r="979" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B979" s="54"/>
-      <c r="C979" s="55"/>
+      <c r="B979" s="41"/>
+      <c r="C979" s="42"/>
     </row>
     <row r="980" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B980" s="54"/>
-      <c r="C980" s="55"/>
+      <c r="B980" s="41"/>
+      <c r="C980" s="42"/>
     </row>
     <row r="981" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B981" s="54"/>
-      <c r="C981" s="55"/>
+      <c r="B981" s="41"/>
+      <c r="C981" s="42"/>
     </row>
     <row r="982" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B982" s="54"/>
-      <c r="C982" s="55"/>
+      <c r="B982" s="41"/>
+      <c r="C982" s="42"/>
     </row>
     <row r="983" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B983" s="54"/>
-      <c r="C983" s="55"/>
+      <c r="B983" s="41"/>
+      <c r="C983" s="42"/>
     </row>
     <row r="984" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B984" s="54"/>
-      <c r="C984" s="55"/>
+      <c r="B984" s="41"/>
+      <c r="C984" s="42"/>
     </row>
     <row r="985" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B985" s="54"/>
-      <c r="C985" s="55"/>
+      <c r="B985" s="41"/>
+      <c r="C985" s="42"/>
     </row>
     <row r="986" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B986" s="54"/>
-      <c r="C986" s="55"/>
+      <c r="B986" s="41"/>
+      <c r="C986" s="42"/>
     </row>
     <row r="987" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B987" s="54"/>
-      <c r="C987" s="55"/>
+      <c r="B987" s="41"/>
+      <c r="C987" s="42"/>
     </row>
     <row r="988" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B988" s="54"/>
-      <c r="C988" s="55"/>
+      <c r="B988" s="41"/>
+      <c r="C988" s="42"/>
     </row>
     <row r="989" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B989" s="54"/>
-      <c r="C989" s="55"/>
+      <c r="B989" s="41"/>
+      <c r="C989" s="42"/>
     </row>
     <row r="990" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B990" s="54"/>
-      <c r="C990" s="55"/>
+      <c r="B990" s="41"/>
+      <c r="C990" s="42"/>
     </row>
     <row r="991" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B991" s="54"/>
-      <c r="C991" s="55"/>
+      <c r="B991" s="41"/>
+      <c r="C991" s="42"/>
     </row>
     <row r="992" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B992" s="54"/>
-      <c r="C992" s="55"/>
+      <c r="B992" s="41"/>
+      <c r="C992" s="42"/>
     </row>
     <row r="993" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B993" s="54"/>
-      <c r="C993" s="55"/>
+      <c r="B993" s="41"/>
+      <c r="C993" s="42"/>
     </row>
     <row r="994" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B994" s="54"/>
-      <c r="C994" s="55"/>
+      <c r="B994" s="41"/>
+      <c r="C994" s="42"/>
     </row>
     <row r="995" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B995" s="54"/>
-      <c r="C995" s="55"/>
+      <c r="B995" s="41"/>
+      <c r="C995" s="42"/>
     </row>
     <row r="996" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B996" s="54"/>
-      <c r="C996" s="55"/>
+      <c r="B996" s="41"/>
+      <c r="C996" s="42"/>
     </row>
     <row r="997" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B997" s="54"/>
-      <c r="C997" s="55"/>
+      <c r="B997" s="41"/>
+      <c r="C997" s="42"/>
     </row>
     <row r="998" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B998" s="54"/>
-      <c r="C998" s="55"/>
+      <c r="B998" s="41"/>
+      <c r="C998" s="42"/>
     </row>
     <row r="999" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B999" s="54"/>
-      <c r="C999" s="55"/>
+      <c r="B999" s="41"/>
+      <c r="C999" s="42"/>
     </row>
     <row r="1000" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B1000" s="54"/>
-      <c r="C1000" s="55"/>
+      <c r="B1000" s="41"/>
+      <c r="C1000" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="2">
